--- a/Antimony_Geerts_all_reaction_details.xlsx
+++ b/Antimony_Geerts_all_reaction_details.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elber\Documents\git\JSON2SBML\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{2F76BDED-321F-4BB6-9AE3-F8C4D5AB12E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{6E0AD208-3927-4B80-9F7C-E088EA910A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-86" yWindow="0" windowWidth="21335" windowHeight="17880" xr2:uid="{B8B61FDB-A028-4FEF-BBDB-A1E25C445D8E}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5176" uniqueCount="1112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5710" uniqueCount="1309">
   <si>
     <t>Species</t>
   </si>
@@ -3040,6 +3040,21 @@
     <t>C_Antibody_unbound_PVS</t>
   </si>
   <si>
+    <t>(fta3 * C_Antibody_unbound_PVS * Abeta40_plaque_unbound_PVS)</t>
+  </si>
+  <si>
+    <t>(fta2 * C_Antibody_unbound_PVS * AB42_Fibril20_PVS)</t>
+  </si>
+  <si>
+    <t>(fta2 * C_Antibody_unbound_PVS * AB42_Fibril24_PVS)</t>
+  </si>
+  <si>
+    <t>(fta0 * C_Antibody_unbound_PVS * AB42_Monomer_PVS)</t>
+  </si>
+  <si>
+    <t>(fta1 * C_Antibody_unbound_PVS * AB42_Oligomer10_PVS)</t>
+  </si>
+  <si>
     <t>PS_Ab_ISF_PVS * Antibody_unbound_ISF / V_PVS * Pe / (exp(Pe) - 1)</t>
   </si>
   <si>
@@ -3049,9 +3064,24 @@
     <t>Antibody_unbound_ISF</t>
   </si>
   <si>
+    <t>(fta2 * Antibody_unbound_ISF * AB42_Fibril20)</t>
+  </si>
+  <si>
+    <t>(fta2 * Antibody_unbound_ISF * AB42_Fibril24)</t>
+  </si>
+  <si>
     <t>(fta0 * Antibody_unbound_ISF * AB42_Monomer)</t>
   </si>
   <si>
+    <t>(fta1 * Antibody_unbound_ISF * AB42_Oligomer02)</t>
+  </si>
+  <si>
+    <t>(fta1 * Antibody_unbound_ISF * AB42_Oligomer10)</t>
+  </si>
+  <si>
+    <t>(fta3 * Antibody_unbound_ISF * AB42_Plaque_unbound)</t>
+  </si>
+  <si>
     <t>PS_Ab_ISF_PVS * C_Antibody_unbound_PVS / vol_brain_ISF * Pe / (exp(Pe) - 1)</t>
   </si>
   <si>
@@ -3356,6 +3386,567 @@
   </si>
   <si>
     <t>((1 - Sigma_ISF_lymph_AB42Mu) * Qbrain_ISF_AB42Mu * AB42_Monomer / Vol_brain_interstitial)</t>
+  </si>
+  <si>
+    <t>AB42_Fibril24</t>
+  </si>
+  <si>
+    <t>k_F23_F24_fortytwo * AB42_Monomer * AB42_Fibril23</t>
+  </si>
+  <si>
+    <t>(k_F24_F23_fortytwo * AB42_Fibril24)</t>
+  </si>
+  <si>
+    <t>(AB42_Fibril24 * Microglia_cell_count * (Microglia_Hi_Fract * Microglia_CL_high_AB42 + (1 - Microglia_Hi_Fract) * Microglia_CL_low_AB42))</t>
+  </si>
+  <si>
+    <t>(k_F24_O12_fortytwo * k_F24_F23_fortytwo * AB42_Fibril24)</t>
+  </si>
+  <si>
+    <t>((1 - sigma_ISF_ABeta42_oligomer024) * Q_PVS * AB42_Fibril24 / vol_brain_ISF)</t>
+  </si>
+  <si>
+    <t>AB42_Fibril24_PVS</t>
+  </si>
+  <si>
+    <t>(1 - sigma_ISF_ABeta42_oligomer024) * Q_PVS * AB42_Fibril24 / V_PVS</t>
+  </si>
+  <si>
+    <t>((1 - sigma_PVS_ABeta42) * Q_PVS * AB42_Fibril24_PVS / V_PVS)</t>
+  </si>
+  <si>
+    <t>AB42_Fibril24_Antibody_bound</t>
+  </si>
+  <si>
+    <t>(AB42_Fibril24_Antibody_bound * Microglia_cell_count * (Microglia_Hi_Fract * Microglia_CL_high_mab + (1 - Microglia_Hi_Fract) * Microglia_CL_low_mAb))</t>
+  </si>
+  <si>
+    <t>fta2 * Antibody_unbound_ISF * AB42_Fibril24</t>
+  </si>
+  <si>
+    <t>AB42_Fibril24_PVS_bound</t>
+  </si>
+  <si>
+    <t>fta2 * C_Antibody_unbound_PVS * AB42_Fibril24_PVS</t>
+  </si>
+  <si>
+    <t>((1 - sigma_PVS_ABeta42_bound) * Q_PVS * AB42_Fibril24_PVS_bound / V_PVS)</t>
+  </si>
+  <si>
+    <t>AB42_Plaque_unbound</t>
+  </si>
+  <si>
+    <t>K_F17_Plaque_fortytwo * AB42_Fibril17 * AB42_Monomer</t>
+  </si>
+  <si>
+    <t>K_F18_Plaque_fortytwo * AB42_Fibril18 * AB42_Monomer</t>
+  </si>
+  <si>
+    <t>K_O13_Plaque_fortytwo * AB42_Oligomer13 * AB42_Monomer</t>
+  </si>
+  <si>
+    <t>K_O14_Plaque_fortytwo * AB42_Oligomer14 * AB42_Monomer</t>
+  </si>
+  <si>
+    <t>K_O15_Plaque_fortytwo * AB42_Oligomer15 * AB42_Monomer</t>
+  </si>
+  <si>
+    <t>K_O16_Plaque_fortytwo * AB42_Oligomer16 * AB42_Monomer</t>
+  </si>
+  <si>
+    <t>(0.5 * AB42_Plaque_unbound * Microglia_cell_count * (Microglia_Hi_Fract * Microglia_CL_high_AB42 + (1 - Microglia_Hi_Fract) * Microglia_CL_low_AB42))</t>
+  </si>
+  <si>
+    <t>AB42_Plaque_Antibody_bound</t>
+  </si>
+  <si>
+    <t>(0.5 * AB42_Plaque_Antibody_bound * Microglia_cell_count * (Microglia_Hi_Fract * Microglia_CL_high_mab + (1 - Microglia_Hi_Fract) * Microglia_CL_low_mAb))</t>
+  </si>
+  <si>
+    <t>fta3 * Antibody_unbound_ISF * AB42_Plaque_unbound</t>
+  </si>
+  <si>
+    <t>Abeta40_plaque_bound_PVS</t>
+  </si>
+  <si>
+    <t>fta3 * C_Antibody_unbound_PVS * Abeta40_plaque_unbound_PVS</t>
+  </si>
+  <si>
+    <t>Abeta40_plaque_unbound_PVS</t>
+  </si>
+  <si>
+    <t>AB42Mb_Blood_Brain_Barrier_bound</t>
+  </si>
+  <si>
+    <t>(CL_up_brain * fBBB * Vol_brain_ES * (1 - FR) * AB42Mb_Blood_Brain_Barrier_bound / Vol_brain_BBB)</t>
+  </si>
+  <si>
+    <t>(CL_up_brain * fBBB * Vol_brain_ES * FR * AB42Mb_Blood_Brain_Barrier_bound / Vol_brain_BBB)</t>
+  </si>
+  <si>
+    <t>kon_FcRn * AB42Mb_Blood_Brain_Barrier_unbound * FcRn_free_BBB</t>
+  </si>
+  <si>
+    <t>(koff_FcRn * AB42Mb_Blood_Brain_Barrier_bound)</t>
+  </si>
+  <si>
+    <t>AB42Mb_Blood_Brain_Barrier_unbound</t>
+  </si>
+  <si>
+    <t>CL_up_brain * fBBB * Vol_brain_ES * AB42Mb_Brain_Plasma / Vol_brain_BBB</t>
+  </si>
+  <si>
+    <t>CL_up_brain * fBBB * Vol_brain_ES * AB42_monomer_Antibody_bound / Vol_brain_BBB</t>
+  </si>
+  <si>
+    <t>(kdeg * AB42Mb_Blood_Brain_Barrier_unbound)</t>
+  </si>
+  <si>
+    <t>fta0 * AB42Mu_Blood_Brain_Barrier * PK_Blood_Brain_Barrier_unbound</t>
+  </si>
+  <si>
+    <t>AB42Mb_Blood_CSF_Barrier_bound</t>
+  </si>
+  <si>
+    <t>(CL_up_brain * (1 - fBBB) * Vol_brain_ES * FR * AB42Mb_Blood_CSF_Barrier_bound / Vol_brain_BCSFB)</t>
+  </si>
+  <si>
+    <t>(f_LV * CL_up_brain * (1 - fBBB) * Vol_brain_ES * (1 - FR) * AB42Mb_Blood_CSF_Barrier_bound / Vol_brain_BCSFB)</t>
+  </si>
+  <si>
+    <t>((1 - f_LV) * CL_up_brain * (1 - fBBB) * Vol_brain_ES * (1 - FR) * AB42Mb_Blood_CSF_Barrier_bound / Vol_brain_BCSFB)</t>
+  </si>
+  <si>
+    <t>kon_FcRn * AB42Mb_Blood_CSF_Barrier_unbound * FcRn_free_BcsfB</t>
+  </si>
+  <si>
+    <t>(koff_FcRn * AB42Mb_Blood_CSF_Barrier_bound)</t>
+  </si>
+  <si>
+    <t>AB42Mb_Blood_CSF_Barrier_unbound</t>
+  </si>
+  <si>
+    <t>CL_up_brain * FBcsfB * Vol_brain_ES * AB42Mb_Brain_Plasma / Vol_brain_BCSFB</t>
+  </si>
+  <si>
+    <t>(1 - f_LV) * CL_up_brain * (1 - fBBB) * Vol_brain_ES * AB42Mb_CSF_TFV / Vol_brain_BCSFB</t>
+  </si>
+  <si>
+    <t>f_LV * CL_up_brain * (1 - fBBB) * Vol_brain_ES * AB42Mb_CSF_LV / Vol_brain_BCSFB</t>
+  </si>
+  <si>
+    <t>(kdeg * AB42Mb_Blood_CSF_Barrier_unbound)</t>
+  </si>
+  <si>
+    <t>fta0 * AB42Mu_Blood_CSF_Barrier * PK_Blood_CSF_Barrier_unbound</t>
+  </si>
+  <si>
+    <t>AB42Mb_Brain_Plasma</t>
+  </si>
+  <si>
+    <t>CL_up_brain * fBBB * Vol_brain_ES * FR * AB42Mb_Blood_Brain_Barrier_bound / Vol_brain_plasma</t>
+  </si>
+  <si>
+    <t>CL_up_brain * (1 - fBBB) * Vol_brain_ES * FR * AB42Mb_Blood_CSF_Barrier_bound / Vol_brain_plasma</t>
+  </si>
+  <si>
+    <t>(CL_up_brain * Vol_brain_ES * AB42Mb_Brain_Plasma / Vol_brain_plasma)</t>
+  </si>
+  <si>
+    <t>Qbrain_plasma * (AB42Mb_central_compartment / PK_Vcent) / Vol_brain_plasma</t>
+  </si>
+  <si>
+    <t>((Qbrain_plasma - Qlymph_Brain) * AB42Mb_Brain_Plasma / Vol_brain_plasma)</t>
+  </si>
+  <si>
+    <t>((1 - Sigma_v_bcsfb) * Qbrain_CSF_AB42Mb * AB42Mb_Brain_Plasma / Vol_brain_plasma)</t>
+  </si>
+  <si>
+    <t>((1 - Sigma_v_isf) * Qbrain_ISF_AB42Mb * AB42Mb_Brain_Plasma / Vol_brain_plasma)</t>
+  </si>
+  <si>
+    <t>fta0 * AB42Mu_Brain_Plasma * PK_Brain_Plasma</t>
+  </si>
+  <si>
+    <t>AB42Mb_CSF_CM</t>
+  </si>
+  <si>
+    <t>(Qbrain_CSF_AB42Mb + Qbrain_ISF_AB42Mb) * AB42Mb_CSF_TFV / Vol_brain_CSFCM</t>
+  </si>
+  <si>
+    <t>((Qbrain_CSF_AB42Mb + Qbrain_ISF_AB42Mb) * AB42Mb_CSF_CM / Vol_brain_CSFCM)</t>
+  </si>
+  <si>
+    <t>fta0 * AB42Mu_CSF_CM * PK_CSF_CM</t>
+  </si>
+  <si>
+    <t>AB42_monomer_Antibody_bound</t>
+  </si>
+  <si>
+    <t>(AB42_monomer_Antibody_bound * Microglia_cell_count * (Microglia_Hi_Fract * Microglia_CL_high_mab + (1 - Microglia_Hi_Fract) * Microglia_CL_low_mAb))</t>
+  </si>
+  <si>
+    <t>fta0 * Antibody_unbound_ISF * AB42_Monomer</t>
+  </si>
+  <si>
+    <t>CL_up_brain * fBBB * Vol_brain_ES * (1 - FR) * AB42Mb_Blood_Brain_Barrier_bound / Vol_brain_interstitial</t>
+  </si>
+  <si>
+    <t>(CL_up_brain * fBBB * Vol_brain_ES * AB42_monomer_Antibody_bound / Vol_brain_interstitial)</t>
+  </si>
+  <si>
+    <t>(1 - Sigma_v_isf) * Qbrain_ISF_AB42Mb * AB42Mb_Brain_Plasma / Vol_brain_interstitial</t>
+  </si>
+  <si>
+    <t>Qbrain_ISF_AB42Mb * AB42Mb_CSF_SAS / Vol_brain_interstitial</t>
+  </si>
+  <si>
+    <t>((1 - f_LV) * Qbrain_ISF_AB42Mb * AB42_monomer_Antibody_bound / Vol_brain_interstitial)</t>
+  </si>
+  <si>
+    <t>((1 - Sigma_ISF_lymph) * Qbrain_ISF_AB42Mb * AB42_monomer_Antibody_bound / Vol_brain_interstitial)</t>
+  </si>
+  <si>
+    <t>(f_LV * Qbrain_ISF_AB42Mb * AB42_monomer_Antibody_bound / Vol_brain_interstitial)</t>
+  </si>
+  <si>
+    <t>AB42Mb_CSF_LV</t>
+  </si>
+  <si>
+    <t>f_LV * CL_up_brain * (1 - fBBB) * Vol_brain_ES * (1 - FR) * AB42Mb_Blood_CSF_Barrier_bound / Vol_brain_CSFLV</t>
+  </si>
+  <si>
+    <t>(f_LV * CL_up_brain * (1 - fBBB) * Vol_brain_ES * AB42Mb_CSF_LV / Vol_brain_CSFLV)</t>
+  </si>
+  <si>
+    <t>(f_LV * (Qbrain_CSF_AB42Mb + Qbrain_ISF_AB42Mb) * AB42Mb_CSF_LV / Vol_brain_CSFLV)</t>
+  </si>
+  <si>
+    <t>f_LV * Qbrain_ISF_AB42Mb * AB42_monomer_Antibody_bound / Vol_brain_CSFLV</t>
+  </si>
+  <si>
+    <t>(1 - Sigma_v_bcsfb) * Qbrain_CSF_AB42Mb * f_LV * AB42Mb_Brain_Plasma / Vol_brain_CSFLV</t>
+  </si>
+  <si>
+    <t>fta0 * AB42Mu_CSF_LV * PK_CSF_LV</t>
+  </si>
+  <si>
+    <t>AB42Mb_CSF_SAS</t>
+  </si>
+  <si>
+    <t>(Qbrain_CSF_AB42Mb + Qbrain_ISF_AB42Mb) * AB42Mb_CSF_CM / Vol_brain_CSFSAS</t>
+  </si>
+  <si>
+    <t>((1 - Sigma_CSFSAS_Lymph) * Qbrain_CSF_AB42Mb * AB42Mb_CSF_SAS / Vol_brain_CSFSAS)</t>
+  </si>
+  <si>
+    <t>(Qbrain_ISF_AB42Mb * AB42Mb_CSF_SAS / Vol_brain_CSFSAS)</t>
+  </si>
+  <si>
+    <t>fta0 * AB42Mu_CSF_SAS * PK_CSF_SAS</t>
+  </si>
+  <si>
+    <t>AB42Mb_CSF_TFV</t>
+  </si>
+  <si>
+    <t>(1 - f_LV) * CL_up_brain * (1 - fBBB) * Vol_brain_ES * (1 - FR) * AB42Mb_Blood_CSF_Barrier_bound / Vol_brain_CSFTFV</t>
+  </si>
+  <si>
+    <t>((1 - f_LV) * CL_up_brain * (1 - fBBB) * Vol_brain_ES * AB42Mb_CSF_TFV / Vol_brain_CSFTFV)</t>
+  </si>
+  <si>
+    <t>f_LV * (Qbrain_CSF_AB42Mb + Qbrain_ISF_AB42Mb) * AB42Mb_CSF_LV / Vol_brain_CSFTFV</t>
+  </si>
+  <si>
+    <t>((Qbrain_CSF_AB42Mb + Qbrain_ISF_AB42Mb) * AB42Mb_CSF_TFV / Vol_brain_CSFTFV)</t>
+  </si>
+  <si>
+    <t>(1 - f_LV) * Qbrain_ISF_AB42Mb * AB42_monomer_Antibody_bound / Vol_brain_CSFTFV</t>
+  </si>
+  <si>
+    <t>(1 - Sigma_v_bcsfb) * Qbrain_CSF_AB42Mb * (1 - f_LV) * AB42Mb_Brain_Plasma / Vol_brain_CSFTFV</t>
+  </si>
+  <si>
+    <t>fta0 * AB42Mu_CSF_TFV * PK_CSF_TFV</t>
+  </si>
+  <si>
+    <t>AB42_Monomer_PVS_bound</t>
+  </si>
+  <si>
+    <t>fta0 * C_Antibody_unbound_PVS * AB42_Monomer_PVS</t>
+  </si>
+  <si>
+    <t>((1 - sigma_PVS_ABeta42_bound) * Q_PVS * AB42_Monomer_PVS_bound / V_PVS)</t>
+  </si>
+  <si>
+    <t>AB42Mb_central_compartment</t>
+  </si>
+  <si>
+    <t>(1 - Sigma_CSFSAS_Lymph) * Qbrain_CSF_AB42Mb * AB42Mb_CSF_SAS</t>
+  </si>
+  <si>
+    <t>(PK_CLd2 * AB42Mb_central_compartment / PK_Vcent)</t>
+  </si>
+  <si>
+    <t>PK_CLd2 * AB42Mb_peripheral_compartment / PK_Vper</t>
+  </si>
+  <si>
+    <t>(PK_CL / PK_Vcent * AB42Mb_central_compartment)</t>
+  </si>
+  <si>
+    <t>(Qbrain_plasma - Qlymph_Brain) * AB42Mb_Brain_Plasma</t>
+  </si>
+  <si>
+    <t>(Qbrain_plasma * AB42Mb_central_compartment / PK_Vcent)</t>
+  </si>
+  <si>
+    <t>fta0 * (AB42Mu_central_compartment / AB42Mu_Vcent) * (PK_central_compartment / PK_Vcent) * PK_Vcent</t>
+  </si>
+  <si>
+    <t>(1 - sigma_PVS_ABeta42_bound) * Q_PVS * AB42_Monomer_PVS_bound</t>
+  </si>
+  <si>
+    <t>(1 - Sigma_ISF_lymph) * Qbrain_ISF_AB42Mb * AB42_monomer_Antibody_bound</t>
+  </si>
+  <si>
+    <t>AB42Mb_peripheral_compartment</t>
+  </si>
+  <si>
+    <t>PK_CLd2 * AB42Mb_central_compartment / PK_Vcent</t>
+  </si>
+  <si>
+    <t>(PK_CLd2 * AB42Mb_peripheral_compartment / PK_Vper)</t>
+  </si>
+  <si>
+    <t>AB42Mu_central_compartment</t>
+  </si>
+  <si>
+    <t>AB42Mu_systemic_synthesis_rate</t>
+  </si>
+  <si>
+    <t>(fta0 * (AB42Mu_central_compartment / AB42Mu_Vcent) * (PK_central_compartment / PK_Vcent) * AB40Mu_Vcent)</t>
+  </si>
+  <si>
+    <t>(1 - Sigma_CSFSAS_Lymph_AB42Mu) * Qbrain_CSF_AB42Mu * AB42Mu_CSF_SAS</t>
+  </si>
+  <si>
+    <t>(AB42Mu_CLd2 * AB42Mu_central_compartment / AB42Mu_Vcent)</t>
+  </si>
+  <si>
+    <t>AB42Mu_CLd2 * AB42Mu_peripheral_compartment / AB42Mu_Vper</t>
+  </si>
+  <si>
+    <t>(AB42Mu_CL / AB42Mu_Vcent * AB42Mu_central_compartment)</t>
+  </si>
+  <si>
+    <t>(Qbrain_plasma - Qlymph_Brain) * AB42Mu_Brain_Plasma</t>
+  </si>
+  <si>
+    <t>(Qbrain_plasma * AB42Mu_central_compartment / AB42Mu_Vcent)</t>
+  </si>
+  <si>
+    <t>(1 - sigma_PVS_ABeta42) * Q_PVS * AB42_Monomer_PVS</t>
+  </si>
+  <si>
+    <t>(1 - Sigma_ISF_lymph_AB42Mu) * Qbrain_ISF_AB42Mu * AB42_Monomer</t>
+  </si>
+  <si>
+    <t>AB42Mu_peripheral_compartment</t>
+  </si>
+  <si>
+    <t>AB42Mu_CLd2 * AB42Mu_central_compartment / AB42Mu_Vcent</t>
+  </si>
+  <si>
+    <t>(AB42Mu_CLd2 * AB42Mu_peripheral_compartment / AB42Mu_Vper)</t>
+  </si>
+  <si>
+    <t>AB42_Fibril20</t>
+  </si>
+  <si>
+    <t>k_F19_F20_fortytwo * AB42_Monomer * AB42_Fibril19</t>
+  </si>
+  <si>
+    <t>(k_F20_F19_fortytwo * AB42_Fibril20)</t>
+  </si>
+  <si>
+    <t>(AB42_Fibril20 * Microglia_cell_count * (Microglia_Hi_Fract * Microglia_CL_high_AB42 + (1 - Microglia_Hi_Fract) * Microglia_CL_low_AB42))</t>
+  </si>
+  <si>
+    <t>((1 - sigma_ISF_ABeta42_oligomer020) * Q_PVS * AB42_Fibril20 / vol_brain_ISF)</t>
+  </si>
+  <si>
+    <t>AB42_Fibril20_PVS</t>
+  </si>
+  <si>
+    <t>(1 - sigma_ISF_ABeta42_oligomer020) * Q_PVS * AB42_Fibril20 / V_PVS</t>
+  </si>
+  <si>
+    <t>((1 - sigma_PVS_ABeta42) * Q_PVS * AB42_Fibril20_PVS / V_PVS)</t>
+  </si>
+  <si>
+    <t>AB42_Fibril20_PVS_bound</t>
+  </si>
+  <si>
+    <t>fta2 * C_Antibody_unbound_PVS * AB42_Fibril20_PVS</t>
+  </si>
+  <si>
+    <t>((1 - sigma_PVS_ABeta42_bound) * Q_PVS * AB42_Fibril20_PVS_bound / V_PVS)</t>
+  </si>
+  <si>
+    <t>AB42_Oligomer02</t>
+  </si>
+  <si>
+    <t>k_M_O2_fortytwo * AB42_Monomer * AB42_Monomer</t>
+  </si>
+  <si>
+    <t>k_M_O2_fortytwo * AB42_Plaque_Driven_Monomer_Addition_Vmax * AB42_Monomer * AB42_Monomer * (AB42_Plaque_unbound / (AB42_Plaque_unbound + AB42_Plaque_Driven_Monomer_Addition_EC50))</t>
+  </si>
+  <si>
+    <t>(k_O2_M_fortytwo * AB42_Oligomer02)</t>
+  </si>
+  <si>
+    <t>((1 - sigma_ISF_ABeta42_oligomer02) * Q_PVS * AB42_Oligomer02 / vol_brain_ISF)</t>
+  </si>
+  <si>
+    <t>AB42Mu_CSF_LV</t>
+  </si>
+  <si>
+    <t>(f_LV * CL_up_brain_AB42Mu * (1 - fBBB) * Vol_brain_ES * AB42Mu_CSF_LV / Vol_brain_CSFLV)</t>
+  </si>
+  <si>
+    <t>(f_LV * (Qbrain_CSF_AB42Mu + Qbrain_ISF_AB42Mu) * AB42Mu_CSF_LV / Vol_brain_CSFLV)</t>
+  </si>
+  <si>
+    <t>f_LV * Qbrain_ISF_AB42Mu * AB42_Monomer / Vol_brain_CSFLV</t>
+  </si>
+  <si>
+    <t>(1 - Sigma_v_bcsfb_AB42Mu) * Qbrain_CSF_AB42Mu * f_LV * AB42Mu_Brain_Plasma / Vol_brain_CSFLV</t>
+  </si>
+  <si>
+    <t>AB42_Monomer_PVS</t>
+  </si>
+  <si>
+    <t>(1 - sigma_ISF_ABeta42_monomer) * Q_PVS * AB42_Monomer / V_PVS</t>
+  </si>
+  <si>
+    <t>((1 - sigma_PVS_ABeta42) * Q_PVS * AB42_Monomer_PVS / V_PVS)</t>
+  </si>
+  <si>
+    <t>AB42Mu_CSF_SAS</t>
+  </si>
+  <si>
+    <t>(Qbrain_CSF_AB42Mu + Qbrain_ISF_AB42Mu) * AB42Mu_CSF_CM / Vol_brain_CSFSAS</t>
+  </si>
+  <si>
+    <t>((1 - Sigma_CSFSAS_Lymph_AB42Mu) * Qbrain_CSF_AB42Mu * AB42Mu_CSF_SAS / Vol_brain_CSFSAS)</t>
+  </si>
+  <si>
+    <t>(Qbrain_ISF_AB42Mu * AB42Mu_CSF_SAS / Vol_brain_CSFSAS)</t>
+  </si>
+  <si>
+    <t>AB42Mu_CSF_TFV</t>
+  </si>
+  <si>
+    <t>((1 - f_LV) * CL_up_brain * (1 - fBBB) * Vol_brain_ES * AB42Mu_CSF_TFV / Vol_brain_CSFTFV)</t>
+  </si>
+  <si>
+    <t>f_LV * (Qbrain_CSF_AB42Mu + Qbrain_ISF_AB42Mu) * AB42Mu_CSF_LV / Vol_brain_CSFTFV</t>
+  </si>
+  <si>
+    <t>((Qbrain_CSF_AB42Mu + Qbrain_ISF_AB42Mu) * AB42Mu_CSF_TFV / Vol_brain_CSFTFV)</t>
+  </si>
+  <si>
+    <t>(1 - Sigma_v_bcsfb_AB42Mu) * Qbrain_CSF_AB42Mu * (1 - f_LV) * AB42Mu_Brain_Plasma / Vol_brain_CSFTFV</t>
+  </si>
+  <si>
+    <t>(1 - f_LV) * Qbrain_ISF_AB42Mu * AB42_Monomer / Vol_brain_CSFTFV</t>
+  </si>
+  <si>
+    <t>AB42Mu_CSF_CM</t>
+  </si>
+  <si>
+    <t>(Qbrain_CSF_AB42Mu + Qbrain_ISF_AB42Mu) * AB42Mu_CSF_TFV / Vol_brain_CSFCM</t>
+  </si>
+  <si>
+    <t>((Qbrain_CSF_AB42Mu + Qbrain_ISF_AB42Mu) * AB42Mu_CSF_CM / Vol_brain_CSFCM)</t>
+  </si>
+  <si>
+    <t>AB42Mu_Brain_Plasma</t>
+  </si>
+  <si>
+    <t>(CL_up_brain_AB42Mu * Vol_brain_ES * AB42Mu_Brain_Plasma / Vol_brain_plasma)</t>
+  </si>
+  <si>
+    <t>Qbrain_plasma * (AB42Mu_central_compartment / AB42Mu_Vcent) / Vol_brain_plasma</t>
+  </si>
+  <si>
+    <t>((Qbrain_plasma - Qlymph_Brain) * AB42Mu_Brain_Plasma / Vol_brain_plasma)</t>
+  </si>
+  <si>
+    <t>((1 - Sigma_v_bcsfb_AB42Mu) * Qbrain_CSF_AB42Mu * AB42Mu_Brain_Plasma / Vol_brain_plasma)</t>
+  </si>
+  <si>
+    <t>((1 - Sigma_v_isf_AB42Mu) * Qbrain_ISF_AB42Mu * AB42Mu_Brain_Plasma / Vol_brain_plasma)</t>
+  </si>
+  <si>
+    <t>AB42Mu_Blood_CSF_Barrier</t>
+  </si>
+  <si>
+    <t>CL_up_brain_AB42Mu * FBcsfB * Vol_brain_ES * AB42Mu_Brain_Plasma / Vol_brain_BCSFB</t>
+  </si>
+  <si>
+    <t>f_LV * CL_up_brain_AB42Mu * (1 - fBBB) * Vol_brain_ES * AB42Mu_CSF_LV / Vol_brain_BCSFB</t>
+  </si>
+  <si>
+    <t>(1 - f_LV) * CL_up_brain_AB42Mu * (1 - fBBB) * Vol_brain_ES * AB42Mu_CSF_TFV / Vol_brain_BCSFB</t>
+  </si>
+  <si>
+    <t>(kdeg_AB42Mu * AB42Mu_Blood_CSF_Barrier)</t>
+  </si>
+  <si>
+    <t>AB42Mu_Blood_Brain_Barrier</t>
+  </si>
+  <si>
+    <t>CL_up_brain_AB42Mu * fBBB * Vol_brain_ES * AB42_Monomer / Vol_brain_BBB</t>
+  </si>
+  <si>
+    <t>CL_up_brain_AB42Mu * fBBB * Vol_brain_ES * AB42Mu_Brain_Plasma / Vol_brain_BBB</t>
+  </si>
+  <si>
+    <t>(kdeg_AB42Mu * AB42Mu_Blood_Brain_Barrier)</t>
+  </si>
+  <si>
+    <t>AB42_Oligomer10</t>
+  </si>
+  <si>
+    <t>k_O9_O10_fortytwo * AB42_Monomer * AB42_Oligomer09</t>
+  </si>
+  <si>
+    <t>(k_O10_O9_fortytwo * AB42_Oligomer10)</t>
+  </si>
+  <si>
+    <t>k_O9_O10_fortytwo * AB42_Plaque_Driven_Monomer_Addition_Vmax * AB42_Monomer * AB42_Oligomer09 * (AB42_Plaque_unbound / (AB42_Plaque_unbound + AB42_Plaque_Driven_Monomer_Addition_EC50))</t>
+  </si>
+  <si>
+    <t>(AB42_Oligomer10 * Microglia_cell_count * (Microglia_Hi_Fract * Microglia_CL_high_AB42 + (1 - Microglia_Hi_Fract) * Microglia_CL_low_AB42))</t>
+  </si>
+  <si>
+    <t>((1 - sigma_ISF_ABeta42_oligomer010) * Q_PVS * AB42_Oligomer10 / vol_brain_ISF)</t>
+  </si>
+  <si>
+    <t>AB42_Oligomer10_PVS</t>
+  </si>
+  <si>
+    <t>(1 - sigma_ISF_ABeta42_oligomer010) * Q_PVS * AB42_Oligomer10 / V_PVS</t>
+  </si>
+  <si>
+    <t>((1 - sigma_PVS_ABeta42) * Q_PVS * AB42_Oligomer10_PVS / V_PVS)</t>
+  </si>
+  <si>
+    <t>AB42_Oligomer10_PVS_bound</t>
+  </si>
+  <si>
+    <t>((1 - sigma_PVS_ABeta42_bound) * Q_PVS * AB42_Oligomer10_PVS_bound / V_PVS)</t>
   </si>
 </sst>
 </file>
@@ -4254,7 +4845,7 @@
   <dimension ref="A1:N1557"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="20.4609375" customWidth="1"/>
+    <col min="1" max="1" width="27.3828125" customWidth="1"/>
     <col min="2" max="2" width="3.23046875" customWidth="1"/>
     <col min="3" max="3" width="2.23046875" customWidth="1"/>
     <col min="12" max="12" width="25.23046875" customWidth="1"/>
@@ -11479,7 +12070,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="657" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="657" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A657" t="s">
         <v>431</v>
       </c>
@@ -11490,7 +12081,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="658" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="658" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A658" t="s">
         <v>431</v>
       </c>
@@ -11501,7 +12092,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="659" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="659" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A659" t="s">
         <v>431</v>
       </c>
@@ -11512,7 +12103,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="660" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="660" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A660" t="s">
         <v>431</v>
       </c>
@@ -11523,7 +12114,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="661" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="661" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A661" t="s">
         <v>431</v>
       </c>
@@ -11534,7 +12125,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="662" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="662" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A662" t="s">
         <v>431</v>
       </c>
@@ -11545,7 +12136,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="663" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="663" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A663" t="s">
         <v>431</v>
       </c>
@@ -11556,7 +12147,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="664" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="664" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A664" t="s">
         <v>431</v>
       </c>
@@ -11567,7 +12158,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="665" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="665" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A665" t="s">
         <v>435</v>
       </c>
@@ -11578,7 +12169,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="666" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="666" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A666" t="s">
         <v>435</v>
       </c>
@@ -11589,7 +12180,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="667" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="667" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A667" t="s">
         <v>435</v>
       </c>
@@ -11600,7 +12191,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="668" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="668" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A668" t="s">
         <v>438</v>
       </c>
@@ -11611,7 +12202,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="669" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="669" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A669" t="s">
         <v>438</v>
       </c>
@@ -11622,7 +12213,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="670" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="670" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A670" t="s">
         <v>440</v>
       </c>
@@ -11633,7 +12224,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="671" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="671" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A671" t="s">
         <v>441</v>
       </c>
@@ -11644,106 +12235,187 @@
         <v>437</v>
       </c>
     </row>
-    <row r="672" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="672" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A672" t="s">
         <v>442</v>
       </c>
       <c r="B672" t="s">
         <v>5</v>
       </c>
-      <c r="D672" t="s">
+      <c r="D672" s="1" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="673" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L672" t="s">
+        <v>1298</v>
+      </c>
+      <c r="M672" t="s">
+        <v>5</v>
+      </c>
+      <c r="N672" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="673" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A673" t="s">
         <v>442</v>
       </c>
       <c r="B673" t="s">
         <v>7</v>
       </c>
-      <c r="D673" t="s">
+      <c r="D673" s="1" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="674" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L673" t="s">
+        <v>1298</v>
+      </c>
+      <c r="M673" t="s">
+        <v>7</v>
+      </c>
+      <c r="N673" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="674" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A674" t="s">
         <v>442</v>
       </c>
       <c r="B674" t="s">
         <v>7</v>
       </c>
-      <c r="D674" t="s">
+      <c r="D674" s="1" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="675" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L674" t="s">
+        <v>1298</v>
+      </c>
+      <c r="M674" t="s">
+        <v>7</v>
+      </c>
+      <c r="N674" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="675" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A675" t="s">
         <v>442</v>
       </c>
       <c r="B675" t="s">
         <v>5</v>
       </c>
-      <c r="D675" t="s">
+      <c r="D675" s="1" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="676" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L675" t="s">
+        <v>1298</v>
+      </c>
+      <c r="M675" t="s">
+        <v>5</v>
+      </c>
+      <c r="N675" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="676" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A676" t="s">
         <v>442</v>
       </c>
       <c r="B676" t="s">
         <v>5</v>
       </c>
-      <c r="D676" t="s">
+      <c r="D676" s="1" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="677" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L676" t="s">
+        <v>1298</v>
+      </c>
+      <c r="M676" t="s">
+        <v>5</v>
+      </c>
+      <c r="N676" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="677" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A677" t="s">
         <v>442</v>
       </c>
       <c r="B677" t="s">
         <v>7</v>
       </c>
-      <c r="D677" t="s">
+      <c r="D677" s="1" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="678" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L677" t="s">
+        <v>1298</v>
+      </c>
+      <c r="M677" t="s">
+        <v>7</v>
+      </c>
+      <c r="N677" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="678" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A678" t="s">
         <v>442</v>
       </c>
       <c r="B678" t="s">
         <v>7</v>
       </c>
-      <c r="D678" t="s">
+      <c r="D678" s="1" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="679" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L678" t="s">
+        <v>1298</v>
+      </c>
+      <c r="M678" t="s">
+        <v>7</v>
+      </c>
+      <c r="N678" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="679" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A679" t="s">
         <v>442</v>
       </c>
       <c r="B679" t="s">
         <v>7</v>
       </c>
-      <c r="D679" t="s">
+      <c r="D679" s="1" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="680" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L679" t="s">
+        <v>1298</v>
+      </c>
+      <c r="M679" t="s">
+        <v>7</v>
+      </c>
+      <c r="N679" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="680" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A680" t="s">
         <v>442</v>
       </c>
       <c r="B680" t="s">
         <v>7</v>
       </c>
-      <c r="D680" t="s">
+      <c r="D680" s="1" t="s">
         <v>451</v>
       </c>
-    </row>
-    <row r="681" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L680" t="s">
+        <v>1298</v>
+      </c>
+      <c r="M680" t="s">
+        <v>7</v>
+      </c>
+      <c r="N680" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="681" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A681" t="s">
         <v>452</v>
       </c>
@@ -11753,8 +12425,17 @@
       <c r="D681" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="682" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L681" t="s">
+        <v>1304</v>
+      </c>
+      <c r="M681" t="s">
+        <v>7</v>
+      </c>
+      <c r="N681" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="682" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A682" t="s">
         <v>452</v>
       </c>
@@ -11764,8 +12445,17 @@
       <c r="D682" t="s">
         <v>451</v>
       </c>
-    </row>
-    <row r="683" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L682" t="s">
+        <v>1304</v>
+      </c>
+      <c r="M682" t="s">
+        <v>5</v>
+      </c>
+      <c r="N682" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="683" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A683" t="s">
         <v>452</v>
       </c>
@@ -11775,8 +12465,17 @@
       <c r="D683" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="684" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L683" t="s">
+        <v>1304</v>
+      </c>
+      <c r="M683" t="s">
+        <v>7</v>
+      </c>
+      <c r="N683" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="684" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A684" t="s">
         <v>455</v>
       </c>
@@ -11787,7 +12486,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="685" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="685" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A685" t="s">
         <v>455</v>
       </c>
@@ -11798,7 +12497,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="686" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="686" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A686" t="s">
         <v>457</v>
       </c>
@@ -11808,9 +12507,18 @@
       <c r="D686" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="687" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A687" t="s">
+      <c r="L686" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="M686" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="N686" s="2" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="687" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A687" s="2" t="s">
         <v>458</v>
       </c>
       <c r="B687" t="s">
@@ -11820,7 +12528,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="688" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="688" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A688" t="s">
         <v>459</v>
       </c>
@@ -13943,7 +14651,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="881" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="881" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A881" t="s">
         <v>585</v>
       </c>
@@ -13954,7 +14662,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="882" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="882" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A882" t="s">
         <v>588</v>
       </c>
@@ -13965,7 +14673,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="883" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="883" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A883" t="s">
         <v>588</v>
       </c>
@@ -13976,7 +14684,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="884" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="884" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A884" t="s">
         <v>590</v>
       </c>
@@ -13987,8 +14695,8 @@
         <v>586</v>
       </c>
     </row>
-    <row r="885" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A885" t="s">
+    <row r="885" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A885" s="2" t="s">
         <v>591</v>
       </c>
       <c r="B885" t="s">
@@ -13998,7 +14706,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="886" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="886" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A886" t="s">
         <v>592</v>
       </c>
@@ -14008,8 +14716,17 @@
       <c r="D886" t="s">
         <v>593</v>
       </c>
-    </row>
-    <row r="887" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L886" t="s">
+        <v>1294</v>
+      </c>
+      <c r="M886" t="s">
+        <v>7</v>
+      </c>
+      <c r="N886" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="887" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A887" t="s">
         <v>592</v>
       </c>
@@ -14019,8 +14736,17 @@
       <c r="D887" t="s">
         <v>594</v>
       </c>
-    </row>
-    <row r="888" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L887" t="s">
+        <v>1294</v>
+      </c>
+      <c r="M887" t="s">
+        <v>5</v>
+      </c>
+      <c r="N887" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="888" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A888" t="s">
         <v>592</v>
       </c>
@@ -14030,8 +14756,17 @@
       <c r="D888" t="s">
         <v>595</v>
       </c>
-    </row>
-    <row r="889" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L888" t="s">
+        <v>1294</v>
+      </c>
+      <c r="M888" t="s">
+        <v>5</v>
+      </c>
+      <c r="N888" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="889" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A889" t="s">
         <v>592</v>
       </c>
@@ -14041,82 +14776,154 @@
       <c r="D889" t="s">
         <v>596</v>
       </c>
-    </row>
-    <row r="890" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L889" t="s">
+        <v>1294</v>
+      </c>
+      <c r="M889" t="s">
+        <v>7</v>
+      </c>
+      <c r="N889" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="890" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A890" t="s">
         <v>597</v>
       </c>
       <c r="B890" t="s">
         <v>7</v>
       </c>
-      <c r="D890" t="s">
+      <c r="D890" s="1" t="s">
         <v>598</v>
       </c>
-    </row>
-    <row r="891" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L890" t="s">
+        <v>1289</v>
+      </c>
+      <c r="M890" t="s">
+        <v>7</v>
+      </c>
+      <c r="N890" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="891" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A891" t="s">
         <v>597</v>
       </c>
       <c r="B891" t="s">
         <v>7</v>
       </c>
-      <c r="D891" t="s">
+      <c r="D891" s="1" t="s">
         <v>599</v>
       </c>
-    </row>
-    <row r="892" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L891" t="s">
+        <v>1289</v>
+      </c>
+      <c r="M891" t="s">
+        <v>5</v>
+      </c>
+      <c r="N891" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="892" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A892" t="s">
         <v>597</v>
       </c>
       <c r="B892" t="s">
         <v>5</v>
       </c>
-      <c r="D892" t="s">
+      <c r="D892" s="1" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="893" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L892" t="s">
+        <v>1289</v>
+      </c>
+      <c r="M892" t="s">
+        <v>5</v>
+      </c>
+      <c r="N892" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="893" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A893" t="s">
         <v>597</v>
       </c>
       <c r="B893" t="s">
         <v>5</v>
       </c>
-      <c r="D893" t="s">
+      <c r="D893" s="1" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="894" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L893" t="s">
+        <v>1289</v>
+      </c>
+      <c r="M893" t="s">
+        <v>5</v>
+      </c>
+      <c r="N893" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="894" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A894" t="s">
         <v>597</v>
       </c>
       <c r="B894" t="s">
         <v>5</v>
       </c>
-      <c r="D894" t="s">
+      <c r="D894" s="1" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="895" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L894" t="s">
+        <v>1289</v>
+      </c>
+      <c r="M894" t="s">
+        <v>7</v>
+      </c>
+      <c r="N894" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="895" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A895" t="s">
         <v>603</v>
       </c>
       <c r="B895" t="s">
         <v>7</v>
       </c>
-      <c r="D895" t="s">
+      <c r="D895" s="1" t="s">
         <v>604</v>
       </c>
-    </row>
-    <row r="896" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L895" t="s">
+        <v>1283</v>
+      </c>
+      <c r="M895" t="s">
+        <v>7</v>
+      </c>
+      <c r="N895" s="1" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="896" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A896" t="s">
         <v>603</v>
       </c>
       <c r="B896" t="s">
         <v>7</v>
       </c>
-      <c r="D896" t="s">
+      <c r="D896" s="1" t="s">
         <v>605</v>
+      </c>
+      <c r="L896" t="s">
+        <v>1283</v>
+      </c>
+      <c r="M896" t="s">
+        <v>7</v>
+      </c>
+      <c r="N896" s="3" t="s">
+        <v>1284</v>
       </c>
     </row>
     <row r="897" spans="1:14" x14ac:dyDescent="0.4">
@@ -14126,8 +14933,17 @@
       <c r="B897" t="s">
         <v>7</v>
       </c>
-      <c r="D897" t="s">
+      <c r="D897" s="3" t="s">
         <v>606</v>
+      </c>
+      <c r="L897" t="s">
+        <v>1283</v>
+      </c>
+      <c r="M897" t="s">
+        <v>5</v>
+      </c>
+      <c r="N897" s="1" t="s">
+        <v>1285</v>
       </c>
     </row>
     <row r="898" spans="1:14" x14ac:dyDescent="0.4">
@@ -14137,8 +14953,17 @@
       <c r="B898" t="s">
         <v>7</v>
       </c>
-      <c r="D898" t="s">
+      <c r="D898" s="3" t="s">
         <v>607</v>
+      </c>
+      <c r="L898" t="s">
+        <v>1283</v>
+      </c>
+      <c r="M898" t="s">
+        <v>7</v>
+      </c>
+      <c r="N898" s="1" t="s">
+        <v>1286</v>
       </c>
     </row>
     <row r="899" spans="1:14" x14ac:dyDescent="0.4">
@@ -14148,8 +14973,17 @@
       <c r="B899" t="s">
         <v>7</v>
       </c>
-      <c r="D899" t="s">
+      <c r="D899" s="1" t="s">
         <v>608</v>
+      </c>
+      <c r="L899" t="s">
+        <v>1283</v>
+      </c>
+      <c r="M899" t="s">
+        <v>7</v>
+      </c>
+      <c r="N899" s="3" t="s">
+        <v>1287</v>
       </c>
     </row>
     <row r="900" spans="1:14" x14ac:dyDescent="0.4">
@@ -14159,8 +14993,17 @@
       <c r="B900" t="s">
         <v>5</v>
       </c>
-      <c r="D900" t="s">
+      <c r="D900" s="1" t="s">
         <v>609</v>
+      </c>
+      <c r="L900" t="s">
+        <v>1283</v>
+      </c>
+      <c r="M900" t="s">
+        <v>7</v>
+      </c>
+      <c r="N900" s="1" t="s">
+        <v>1288</v>
       </c>
     </row>
     <row r="901" spans="1:14" x14ac:dyDescent="0.4">
@@ -14170,7 +15013,7 @@
       <c r="B901" t="s">
         <v>7</v>
       </c>
-      <c r="D901" t="s">
+      <c r="D901" s="3" t="s">
         <v>596</v>
       </c>
     </row>
@@ -14181,7 +15024,7 @@
       <c r="B902" t="s">
         <v>7</v>
       </c>
-      <c r="D902" t="s">
+      <c r="D902" s="3" t="s">
         <v>600</v>
       </c>
     </row>
@@ -14195,6 +15038,15 @@
       <c r="D903" t="s">
         <v>611</v>
       </c>
+      <c r="L903" t="s">
+        <v>1280</v>
+      </c>
+      <c r="M903" t="s">
+        <v>7</v>
+      </c>
+      <c r="N903" t="s">
+        <v>1024</v>
+      </c>
     </row>
     <row r="904" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A904" t="s">
@@ -14206,6 +15058,15 @@
       <c r="D904" t="s">
         <v>612</v>
       </c>
+      <c r="L904" t="s">
+        <v>1280</v>
+      </c>
+      <c r="M904" t="s">
+        <v>5</v>
+      </c>
+      <c r="N904" t="s">
+        <v>1281</v>
+      </c>
     </row>
     <row r="905" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A905" t="s">
@@ -14217,9 +15078,18 @@
       <c r="D905" t="s">
         <v>613</v>
       </c>
+      <c r="L905" t="s">
+        <v>1280</v>
+      </c>
+      <c r="M905" t="s">
+        <v>7</v>
+      </c>
+      <c r="N905" t="s">
+        <v>1282</v>
+      </c>
     </row>
     <row r="906" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A906" t="s">
+      <c r="A906" s="2" t="s">
         <v>614</v>
       </c>
       <c r="B906" t="s">
@@ -14240,13 +15110,13 @@
         <v>617</v>
       </c>
       <c r="L907" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M907" t="s">
         <v>7</v>
       </c>
       <c r="N907" t="s">
-        <v>1035</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="908" spans="1:14" x14ac:dyDescent="0.4">
@@ -14260,13 +15130,13 @@
         <v>617</v>
       </c>
       <c r="L908" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M908" t="s">
         <v>5</v>
       </c>
       <c r="N908" t="s">
-        <v>1036</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="909" spans="1:14" x14ac:dyDescent="0.4">
@@ -14280,13 +15150,13 @@
         <v>618</v>
       </c>
       <c r="L909" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M909" t="s">
         <v>5</v>
       </c>
       <c r="N909" t="s">
-        <v>1037</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="910" spans="1:14" x14ac:dyDescent="0.4">
@@ -14300,13 +15170,13 @@
         <v>618</v>
       </c>
       <c r="L910" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M910" t="s">
         <v>7</v>
       </c>
       <c r="N910" t="s">
-        <v>1038</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="911" spans="1:14" x14ac:dyDescent="0.4">
@@ -14320,13 +15190,13 @@
         <v>619</v>
       </c>
       <c r="L911" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M911" t="s">
         <v>5</v>
       </c>
       <c r="N911" t="s">
-        <v>1039</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="912" spans="1:14" x14ac:dyDescent="0.4">
@@ -14340,13 +15210,13 @@
         <v>620</v>
       </c>
       <c r="L912" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M912" t="s">
         <v>7</v>
       </c>
       <c r="N912" t="s">
-        <v>1040</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="913" spans="1:14" x14ac:dyDescent="0.4">
@@ -14360,13 +15230,13 @@
         <v>621</v>
       </c>
       <c r="L913" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M913" t="s">
         <v>5</v>
       </c>
       <c r="N913" t="s">
-        <v>1041</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="914" spans="1:14" x14ac:dyDescent="0.4">
@@ -14380,13 +15250,13 @@
         <v>622</v>
       </c>
       <c r="L914" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M914" t="s">
         <v>7</v>
       </c>
       <c r="N914" t="s">
-        <v>1042</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="915" spans="1:14" x14ac:dyDescent="0.4">
@@ -14400,13 +15270,13 @@
         <v>623</v>
       </c>
       <c r="L915" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M915" t="s">
         <v>5</v>
       </c>
       <c r="N915" t="s">
-        <v>1043</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="916" spans="1:14" x14ac:dyDescent="0.4">
@@ -14420,13 +15290,13 @@
         <v>624</v>
       </c>
       <c r="L916" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M916" t="s">
         <v>7</v>
       </c>
       <c r="N916" t="s">
-        <v>1044</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="917" spans="1:14" x14ac:dyDescent="0.4">
@@ -14440,13 +15310,13 @@
         <v>625</v>
       </c>
       <c r="L917" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M917" t="s">
         <v>5</v>
       </c>
       <c r="N917" t="s">
-        <v>1045</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="918" spans="1:14" x14ac:dyDescent="0.4">
@@ -14460,13 +15330,13 @@
         <v>626</v>
       </c>
       <c r="L918" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M918" t="s">
         <v>7</v>
       </c>
       <c r="N918" t="s">
-        <v>1046</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="919" spans="1:14" x14ac:dyDescent="0.4">
@@ -14480,13 +15350,13 @@
         <v>627</v>
       </c>
       <c r="L919" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M919" t="s">
         <v>5</v>
       </c>
       <c r="N919" t="s">
-        <v>1047</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="920" spans="1:14" x14ac:dyDescent="0.4">
@@ -14500,13 +15370,13 @@
         <v>628</v>
       </c>
       <c r="L920" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M920" t="s">
         <v>7</v>
       </c>
       <c r="N920" t="s">
-        <v>1048</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="921" spans="1:14" x14ac:dyDescent="0.4">
@@ -14520,13 +15390,13 @@
         <v>629</v>
       </c>
       <c r="L921" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M921" t="s">
         <v>5</v>
       </c>
       <c r="N921" t="s">
-        <v>1049</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="922" spans="1:14" x14ac:dyDescent="0.4">
@@ -14540,13 +15410,13 @@
         <v>630</v>
       </c>
       <c r="L922" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M922" t="s">
         <v>7</v>
       </c>
       <c r="N922" t="s">
-        <v>1052</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="923" spans="1:14" x14ac:dyDescent="0.4">
@@ -14560,13 +15430,13 @@
         <v>631</v>
       </c>
       <c r="L923" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M923" t="s">
         <v>7</v>
       </c>
       <c r="N923" t="s">
-        <v>1053</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="924" spans="1:14" x14ac:dyDescent="0.4">
@@ -14580,13 +15450,13 @@
         <v>632</v>
       </c>
       <c r="L924" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M924" t="s">
         <v>7</v>
       </c>
       <c r="N924" t="s">
-        <v>1054</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="925" spans="1:14" x14ac:dyDescent="0.4">
@@ -14600,13 +15470,13 @@
         <v>443</v>
       </c>
       <c r="L925" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M925" t="s">
         <v>7</v>
       </c>
       <c r="N925" t="s">
-        <v>1055</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="926" spans="1:14" x14ac:dyDescent="0.4">
@@ -14620,13 +15490,13 @@
         <v>444</v>
       </c>
       <c r="L926" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M926" t="s">
         <v>7</v>
       </c>
       <c r="N926" t="s">
-        <v>1056</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="927" spans="1:14" x14ac:dyDescent="0.4">
@@ -14640,13 +15510,13 @@
         <v>445</v>
       </c>
       <c r="L927" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M927" t="s">
         <v>5</v>
       </c>
       <c r="N927" t="s">
-        <v>1057</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="928" spans="1:14" x14ac:dyDescent="0.4">
@@ -14660,13 +15530,13 @@
         <v>446</v>
       </c>
       <c r="L928" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M928" t="s">
         <v>5</v>
       </c>
       <c r="N928" t="s">
-        <v>1058</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="929" spans="1:14" x14ac:dyDescent="0.4">
@@ -14680,13 +15550,13 @@
         <v>460</v>
       </c>
       <c r="L929" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M929" t="s">
         <v>7</v>
       </c>
       <c r="N929" t="s">
-        <v>1059</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="930" spans="1:14" x14ac:dyDescent="0.4">
@@ -14700,13 +15570,13 @@
         <v>461</v>
       </c>
       <c r="L930" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M930" t="s">
         <v>5</v>
       </c>
       <c r="N930" t="s">
-        <v>1060</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="931" spans="1:14" x14ac:dyDescent="0.4">
@@ -14720,13 +15590,13 @@
         <v>474</v>
       </c>
       <c r="L931" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M931" t="s">
         <v>7</v>
       </c>
       <c r="N931" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="932" spans="1:14" x14ac:dyDescent="0.4">
@@ -14740,13 +15610,13 @@
         <v>475</v>
       </c>
       <c r="L932" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M932" t="s">
         <v>5</v>
       </c>
       <c r="N932" t="s">
-        <v>1062</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="933" spans="1:14" x14ac:dyDescent="0.4">
@@ -14760,13 +15630,13 @@
         <v>489</v>
       </c>
       <c r="L933" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M933" t="s">
         <v>7</v>
       </c>
       <c r="N933" t="s">
-        <v>1063</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="934" spans="1:14" x14ac:dyDescent="0.4">
@@ -14780,13 +15650,13 @@
         <v>490</v>
       </c>
       <c r="L934" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M934" t="s">
         <v>5</v>
       </c>
       <c r="N934" t="s">
-        <v>1064</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="935" spans="1:14" x14ac:dyDescent="0.4">
@@ -14800,13 +15670,13 @@
         <v>504</v>
       </c>
       <c r="L935" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M935" t="s">
         <v>7</v>
       </c>
       <c r="N935" t="s">
-        <v>1065</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="936" spans="1:14" x14ac:dyDescent="0.4">
@@ -14820,13 +15690,13 @@
         <v>505</v>
       </c>
       <c r="L936" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M936" t="s">
         <v>5</v>
       </c>
       <c r="N936" t="s">
-        <v>1066</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="937" spans="1:14" x14ac:dyDescent="0.4">
@@ -14840,13 +15710,13 @@
         <v>519</v>
       </c>
       <c r="L937" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M937" t="s">
         <v>7</v>
       </c>
       <c r="N937" t="s">
-        <v>1067</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="938" spans="1:14" x14ac:dyDescent="0.4">
@@ -14860,13 +15730,13 @@
         <v>520</v>
       </c>
       <c r="L938" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M938" t="s">
         <v>5</v>
       </c>
       <c r="N938" t="s">
-        <v>1068</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="939" spans="1:14" x14ac:dyDescent="0.4">
@@ -14880,13 +15750,13 @@
         <v>534</v>
       </c>
       <c r="L939" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M939" t="s">
         <v>7</v>
       </c>
       <c r="N939" t="s">
-        <v>1069</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="940" spans="1:14" x14ac:dyDescent="0.4">
@@ -14900,13 +15770,13 @@
         <v>535</v>
       </c>
       <c r="L940" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M940" t="s">
         <v>5</v>
       </c>
       <c r="N940" t="s">
-        <v>1070</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="941" spans="1:14" x14ac:dyDescent="0.4">
@@ -14920,13 +15790,13 @@
         <v>549</v>
       </c>
       <c r="L941" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M941" t="s">
         <v>7</v>
       </c>
       <c r="N941" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="942" spans="1:14" x14ac:dyDescent="0.4">
@@ -14940,13 +15810,13 @@
         <v>550</v>
       </c>
       <c r="L942" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M942" t="s">
         <v>5</v>
       </c>
       <c r="N942" t="s">
-        <v>1072</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="943" spans="1:14" x14ac:dyDescent="0.4">
@@ -14960,13 +15830,13 @@
         <v>564</v>
       </c>
       <c r="L943" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M943" t="s">
         <v>7</v>
       </c>
       <c r="N943" t="s">
-        <v>1073</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="944" spans="1:14" x14ac:dyDescent="0.4">
@@ -14980,13 +15850,13 @@
         <v>565</v>
       </c>
       <c r="L944" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M944" t="s">
         <v>5</v>
       </c>
       <c r="N944" t="s">
-        <v>1074</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="945" spans="1:14" x14ac:dyDescent="0.4">
@@ -15000,13 +15870,13 @@
         <v>579</v>
       </c>
       <c r="L945" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M945" t="s">
         <v>7</v>
       </c>
       <c r="N945" t="s">
-        <v>1075</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="946" spans="1:14" x14ac:dyDescent="0.4">
@@ -15020,13 +15890,13 @@
         <v>580</v>
       </c>
       <c r="L946" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M946" t="s">
         <v>5</v>
       </c>
       <c r="N946" t="s">
-        <v>1076</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="947" spans="1:14" x14ac:dyDescent="0.4">
@@ -15040,13 +15910,13 @@
         <v>633</v>
       </c>
       <c r="L947" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M947" t="s">
         <v>7</v>
       </c>
       <c r="N947" t="s">
-        <v>1077</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="948" spans="1:14" x14ac:dyDescent="0.4">
@@ -15060,13 +15930,13 @@
         <v>634</v>
       </c>
       <c r="L948" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M948" t="s">
         <v>5</v>
       </c>
       <c r="N948" t="s">
-        <v>1078</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="949" spans="1:14" x14ac:dyDescent="0.4">
@@ -15080,13 +15950,13 @@
         <v>635</v>
       </c>
       <c r="L949" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M949" t="s">
         <v>7</v>
       </c>
       <c r="N949" t="s">
-        <v>1079</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="950" spans="1:14" x14ac:dyDescent="0.4">
@@ -15100,13 +15970,13 @@
         <v>636</v>
       </c>
       <c r="L950" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M950" t="s">
         <v>5</v>
       </c>
       <c r="N950" t="s">
-        <v>1080</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="951" spans="1:14" x14ac:dyDescent="0.4">
@@ -15120,13 +15990,13 @@
         <v>637</v>
       </c>
       <c r="L951" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M951" t="s">
         <v>7</v>
       </c>
       <c r="N951" t="s">
-        <v>1081</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="952" spans="1:14" x14ac:dyDescent="0.4">
@@ -15140,13 +16010,13 @@
         <v>638</v>
       </c>
       <c r="L952" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M952" t="s">
         <v>5</v>
       </c>
       <c r="N952" t="s">
-        <v>1082</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="953" spans="1:14" x14ac:dyDescent="0.4">
@@ -15160,13 +16030,13 @@
         <v>639</v>
       </c>
       <c r="L953" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M953" t="s">
         <v>7</v>
       </c>
       <c r="N953" t="s">
-        <v>1083</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="954" spans="1:14" x14ac:dyDescent="0.4">
@@ -15180,7 +16050,7 @@
         <v>640</v>
       </c>
       <c r="L954" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M954" t="s">
         <v>5</v>
@@ -15193,11 +16063,11 @@
       <c r="B955" t="s">
         <v>7</v>
       </c>
-      <c r="D955" t="s">
+      <c r="D955" s="2" t="s">
         <v>641</v>
       </c>
       <c r="L955" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M955" t="s">
         <v>7</v>
@@ -15210,17 +16080,14 @@
       <c r="B956" t="s">
         <v>7</v>
       </c>
-      <c r="D956" t="s">
+      <c r="D956" s="2" t="s">
         <v>641</v>
       </c>
       <c r="L956" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M956" t="s">
         <v>7</v>
-      </c>
-      <c r="N956" t="s">
-        <v>1084</v>
       </c>
     </row>
     <row r="957" spans="1:14" x14ac:dyDescent="0.4">
@@ -15234,13 +16101,13 @@
         <v>642</v>
       </c>
       <c r="L957" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M957" t="s">
         <v>7</v>
       </c>
       <c r="N957" t="s">
-        <v>1085</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="958" spans="1:14" x14ac:dyDescent="0.4">
@@ -15254,13 +16121,13 @@
         <v>643</v>
       </c>
       <c r="L958" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M958" t="s">
         <v>7</v>
       </c>
       <c r="N958" t="s">
-        <v>1086</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="959" spans="1:14" x14ac:dyDescent="0.4">
@@ -15274,13 +16141,13 @@
         <v>644</v>
       </c>
       <c r="L959" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M959" t="s">
         <v>7</v>
       </c>
       <c r="N959" t="s">
-        <v>1087</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="960" spans="1:14" x14ac:dyDescent="0.4">
@@ -15294,13 +16161,13 @@
         <v>645</v>
       </c>
       <c r="L960" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M960" t="s">
         <v>7</v>
       </c>
       <c r="N960" t="s">
-        <v>1088</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="961" spans="1:14" x14ac:dyDescent="0.4">
@@ -15314,13 +16181,13 @@
         <v>646</v>
       </c>
       <c r="L961" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M961" t="s">
         <v>7</v>
       </c>
       <c r="N961" t="s">
-        <v>1089</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="962" spans="1:14" x14ac:dyDescent="0.4">
@@ -15334,13 +16201,13 @@
         <v>647</v>
       </c>
       <c r="L962" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M962" t="s">
         <v>7</v>
       </c>
       <c r="N962" t="s">
-        <v>1090</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="963" spans="1:14" x14ac:dyDescent="0.4">
@@ -15354,13 +16221,13 @@
         <v>648</v>
       </c>
       <c r="L963" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M963" t="s">
         <v>7</v>
       </c>
       <c r="N963" t="s">
-        <v>1091</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="964" spans="1:14" x14ac:dyDescent="0.4">
@@ -15374,13 +16241,13 @@
         <v>447</v>
       </c>
       <c r="L964" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M964" t="s">
         <v>7</v>
       </c>
       <c r="N964" t="s">
-        <v>1092</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="965" spans="1:14" x14ac:dyDescent="0.4">
@@ -15394,13 +16261,13 @@
         <v>448</v>
       </c>
       <c r="L965" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M965" t="s">
         <v>7</v>
       </c>
       <c r="N965" t="s">
-        <v>1093</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="966" spans="1:14" x14ac:dyDescent="0.4">
@@ -15414,13 +16281,13 @@
         <v>462</v>
       </c>
       <c r="L966" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M966" t="s">
         <v>7</v>
       </c>
       <c r="N966" t="s">
-        <v>1094</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="967" spans="1:14" x14ac:dyDescent="0.4">
@@ -15434,13 +16301,13 @@
         <v>476</v>
       </c>
       <c r="L967" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M967" t="s">
         <v>7</v>
       </c>
       <c r="N967" t="s">
-        <v>1095</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="968" spans="1:14" x14ac:dyDescent="0.4">
@@ -15454,10 +16321,13 @@
         <v>491</v>
       </c>
       <c r="L968" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M968" t="s">
         <v>7</v>
+      </c>
+      <c r="N968" t="s">
+        <v>1105</v>
       </c>
     </row>
     <row r="969" spans="1:14" x14ac:dyDescent="0.4">
@@ -15471,13 +16341,13 @@
         <v>506</v>
       </c>
       <c r="L969" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M969" t="s">
         <v>7</v>
       </c>
       <c r="N969" t="s">
-        <v>1097</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="970" spans="1:14" x14ac:dyDescent="0.4">
@@ -15491,10 +16361,13 @@
         <v>521</v>
       </c>
       <c r="L970" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M970" t="s">
         <v>7</v>
+      </c>
+      <c r="N970" t="s">
+        <v>1109</v>
       </c>
     </row>
     <row r="971" spans="1:14" x14ac:dyDescent="0.4">
@@ -15508,13 +16381,13 @@
         <v>536</v>
       </c>
       <c r="L971" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M971" t="s">
         <v>7</v>
       </c>
       <c r="N971" t="s">
-        <v>1099</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="972" spans="1:14" x14ac:dyDescent="0.4">
@@ -15528,7 +16401,7 @@
         <v>551</v>
       </c>
       <c r="L972" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M972" t="s">
         <v>7</v>
@@ -15545,13 +16418,10 @@
         <v>566</v>
       </c>
       <c r="L973" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M973" t="s">
         <v>7</v>
-      </c>
-      <c r="N973" t="s">
-        <v>1101</v>
       </c>
     </row>
     <row r="974" spans="1:14" x14ac:dyDescent="0.4">
@@ -15565,7 +16435,7 @@
         <v>581</v>
       </c>
       <c r="L974" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M974" t="s">
         <v>7</v>
@@ -15582,7 +16452,7 @@
         <v>649</v>
       </c>
       <c r="L975" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M975" t="s">
         <v>7</v>
@@ -15599,7 +16469,7 @@
         <v>650</v>
       </c>
       <c r="L976" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M976" t="s">
         <v>5</v>
@@ -15616,7 +16486,7 @@
         <v>651</v>
       </c>
       <c r="L977" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M977" t="s">
         <v>7</v>
@@ -15633,7 +16503,7 @@
         <v>652</v>
       </c>
       <c r="L978" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M978" t="s">
         <v>5</v>
@@ -15646,17 +16516,17 @@
       <c r="B979" t="s">
         <v>7</v>
       </c>
-      <c r="D979" t="s">
+      <c r="D979" s="1" t="s">
         <v>653</v>
       </c>
       <c r="L979" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M979" t="s">
         <v>7</v>
       </c>
       <c r="N979" t="s">
-        <v>1009</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="980" spans="1:14" x14ac:dyDescent="0.4">
@@ -15666,17 +16536,17 @@
       <c r="B980" t="s">
         <v>7</v>
       </c>
-      <c r="D980" t="s">
+      <c r="D980" s="1" t="s">
         <v>493</v>
       </c>
       <c r="L980" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M980" t="s">
         <v>7</v>
       </c>
       <c r="N980" t="s">
-        <v>1096</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="981" spans="1:14" x14ac:dyDescent="0.4">
@@ -15686,17 +16556,17 @@
       <c r="B981" t="s">
         <v>7</v>
       </c>
-      <c r="D981" t="s">
+      <c r="D981" s="1" t="s">
         <v>508</v>
       </c>
       <c r="L981" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M981" t="s">
         <v>5</v>
       </c>
       <c r="N981" t="s">
-        <v>1098</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="982" spans="1:14" x14ac:dyDescent="0.4">
@@ -15706,17 +16576,17 @@
       <c r="B982" t="s">
         <v>7</v>
       </c>
-      <c r="D982" t="s">
+      <c r="D982" s="1" t="s">
         <v>523</v>
       </c>
       <c r="L982" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M982" t="s">
         <v>7</v>
       </c>
       <c r="N982" t="s">
-        <v>1100</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="983" spans="1:14" x14ac:dyDescent="0.4">
@@ -15726,17 +16596,17 @@
       <c r="B983" t="s">
         <v>7</v>
       </c>
-      <c r="D983" t="s">
+      <c r="D983" s="1" t="s">
         <v>538</v>
       </c>
       <c r="L983" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M983" t="s">
         <v>7</v>
       </c>
       <c r="N983" t="s">
-        <v>1102</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="984" spans="1:14" x14ac:dyDescent="0.4">
@@ -15746,17 +16616,17 @@
       <c r="B984" t="s">
         <v>7</v>
       </c>
-      <c r="D984" t="s">
+      <c r="D984" s="1" t="s">
         <v>553</v>
       </c>
       <c r="L984" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="M984" t="s">
         <v>7</v>
       </c>
       <c r="N984" t="s">
-        <v>1050</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="985" spans="1:14" x14ac:dyDescent="0.4">
@@ -15766,11 +16636,11 @@
       <c r="B985" t="s">
         <v>7</v>
       </c>
-      <c r="D985" t="s">
+      <c r="D985" s="1" t="s">
         <v>568</v>
       </c>
       <c r="N985" t="s">
-        <v>1051</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="986" spans="1:14" x14ac:dyDescent="0.4">
@@ -15780,8 +16650,11 @@
       <c r="B986" t="s">
         <v>7</v>
       </c>
-      <c r="D986" t="s">
+      <c r="D986" s="1" t="s">
         <v>654</v>
+      </c>
+      <c r="N986" t="s">
+        <v>1118</v>
       </c>
     </row>
     <row r="987" spans="1:14" x14ac:dyDescent="0.4">
@@ -15791,11 +16664,11 @@
       <c r="B987" t="s">
         <v>5</v>
       </c>
-      <c r="D987" t="s">
+      <c r="D987" s="1" t="s">
         <v>655</v>
       </c>
       <c r="N987" t="s">
-        <v>1103</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="988" spans="1:14" x14ac:dyDescent="0.4">
@@ -15805,11 +16678,11 @@
       <c r="B988" t="s">
         <v>7</v>
       </c>
-      <c r="D988" t="s">
+      <c r="D988" s="1" t="s">
         <v>656</v>
       </c>
       <c r="N988" t="s">
-        <v>1104</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="989" spans="1:14" x14ac:dyDescent="0.4">
@@ -15819,11 +16692,11 @@
       <c r="B989" t="s">
         <v>7</v>
       </c>
-      <c r="D989" t="s">
+      <c r="D989" s="1" t="s">
         <v>657</v>
       </c>
       <c r="N989" t="s">
-        <v>1105</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="990" spans="1:14" x14ac:dyDescent="0.4">
@@ -15833,11 +16706,11 @@
       <c r="B990" t="s">
         <v>7</v>
       </c>
-      <c r="D990" t="s">
+      <c r="D990" s="1" t="s">
         <v>658</v>
       </c>
       <c r="N990" t="s">
-        <v>1106</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="991" spans="1:14" x14ac:dyDescent="0.4">
@@ -15847,11 +16720,11 @@
       <c r="B991" t="s">
         <v>7</v>
       </c>
-      <c r="D991" t="s">
+      <c r="D991" s="1" t="s">
         <v>659</v>
       </c>
       <c r="N991" t="s">
-        <v>1107</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="992" spans="1:14" x14ac:dyDescent="0.4">
@@ -15861,11 +16734,11 @@
       <c r="B992" t="s">
         <v>5</v>
       </c>
-      <c r="D992" t="s">
+      <c r="D992" s="1" t="s">
         <v>605</v>
       </c>
       <c r="N992" t="s">
-        <v>1108</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="993" spans="1:14" x14ac:dyDescent="0.4">
@@ -15875,11 +16748,11 @@
       <c r="B993" t="s">
         <v>5</v>
       </c>
-      <c r="D993" t="s">
+      <c r="D993" s="1" t="s">
         <v>660</v>
       </c>
       <c r="N993" t="s">
-        <v>1109</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="994" spans="1:14" x14ac:dyDescent="0.4">
@@ -15889,11 +16762,11 @@
       <c r="B994" t="s">
         <v>7</v>
       </c>
-      <c r="D994" t="s">
+      <c r="D994" s="1" t="s">
         <v>595</v>
       </c>
       <c r="N994" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="995" spans="1:14" x14ac:dyDescent="0.4">
@@ -15903,11 +16776,17 @@
       <c r="B995" t="s">
         <v>7</v>
       </c>
-      <c r="D995" t="s">
+      <c r="D995" s="1" t="s">
         <v>662</v>
       </c>
+      <c r="L995" t="s">
+        <v>1262</v>
+      </c>
+      <c r="M995" t="s">
+        <v>7</v>
+      </c>
       <c r="N995" t="s">
-        <v>1111</v>
+        <v>957</v>
       </c>
     </row>
     <row r="996" spans="1:14" x14ac:dyDescent="0.4">
@@ -15917,8 +16796,17 @@
       <c r="B996" t="s">
         <v>5</v>
       </c>
-      <c r="D996" t="s">
+      <c r="D996" s="1" t="s">
         <v>658</v>
+      </c>
+      <c r="L996" t="s">
+        <v>1262</v>
+      </c>
+      <c r="M996" t="s">
+        <v>7</v>
+      </c>
+      <c r="N996" t="s">
+        <v>1263</v>
       </c>
     </row>
     <row r="997" spans="1:14" x14ac:dyDescent="0.4">
@@ -15928,8 +16816,17 @@
       <c r="B997" t="s">
         <v>5</v>
       </c>
-      <c r="D997" t="s">
+      <c r="D997" s="1" t="s">
         <v>606</v>
+      </c>
+      <c r="L997" t="s">
+        <v>1262</v>
+      </c>
+      <c r="M997" t="s">
+        <v>7</v>
+      </c>
+      <c r="N997" t="s">
+        <v>1264</v>
       </c>
     </row>
     <row r="998" spans="1:14" x14ac:dyDescent="0.4">
@@ -15939,8 +16836,17 @@
       <c r="B998" t="s">
         <v>7</v>
       </c>
-      <c r="D998" t="s">
+      <c r="D998" s="1" t="s">
         <v>663</v>
+      </c>
+      <c r="L998" t="s">
+        <v>1262</v>
+      </c>
+      <c r="M998" t="s">
+        <v>5</v>
+      </c>
+      <c r="N998" t="s">
+        <v>1265</v>
       </c>
     </row>
     <row r="999" spans="1:14" x14ac:dyDescent="0.4">
@@ -15950,8 +16856,17 @@
       <c r="B999" t="s">
         <v>7</v>
       </c>
-      <c r="D999" t="s">
+      <c r="D999" s="1" t="s">
         <v>602</v>
+      </c>
+      <c r="L999" t="s">
+        <v>1262</v>
+      </c>
+      <c r="M999" t="s">
+        <v>5</v>
+      </c>
+      <c r="N999" t="s">
+        <v>1266</v>
       </c>
     </row>
     <row r="1000" spans="1:14" x14ac:dyDescent="0.4">
@@ -15961,8 +16876,17 @@
       <c r="B1000" t="s">
         <v>7</v>
       </c>
-      <c r="D1000" t="s">
+      <c r="D1000" s="1" t="s">
         <v>665</v>
+      </c>
+      <c r="L1000" t="s">
+        <v>1267</v>
+      </c>
+      <c r="M1000" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1000" t="s">
+        <v>1009</v>
       </c>
     </row>
     <row r="1001" spans="1:14" x14ac:dyDescent="0.4">
@@ -15972,8 +16896,17 @@
       <c r="B1001" t="s">
         <v>5</v>
       </c>
-      <c r="D1001" t="s">
+      <c r="D1001" s="1" t="s">
         <v>656</v>
+      </c>
+      <c r="L1001" t="s">
+        <v>1267</v>
+      </c>
+      <c r="M1001" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1001" t="s">
+        <v>1268</v>
       </c>
     </row>
     <row r="1002" spans="1:14" x14ac:dyDescent="0.4">
@@ -15983,8 +16916,17 @@
       <c r="B1002" t="s">
         <v>7</v>
       </c>
-      <c r="D1002" t="s">
+      <c r="D1002" s="1" t="s">
         <v>666</v>
+      </c>
+      <c r="L1002" t="s">
+        <v>1267</v>
+      </c>
+      <c r="M1002" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1002" t="s">
+        <v>1269</v>
       </c>
     </row>
     <row r="1003" spans="1:14" x14ac:dyDescent="0.4">
@@ -15994,8 +16936,17 @@
       <c r="B1003" t="s">
         <v>7</v>
       </c>
-      <c r="D1003" t="s">
+      <c r="D1003" s="1" t="s">
         <v>668</v>
+      </c>
+      <c r="L1003" t="s">
+        <v>1270</v>
+      </c>
+      <c r="M1003" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1003" t="s">
+        <v>965</v>
       </c>
     </row>
     <row r="1004" spans="1:14" x14ac:dyDescent="0.4">
@@ -16005,8 +16956,17 @@
       <c r="B1004" t="s">
         <v>5</v>
       </c>
-      <c r="D1004" t="s">
+      <c r="D1004" s="1" t="s">
         <v>613</v>
+      </c>
+      <c r="L1004" t="s">
+        <v>1270</v>
+      </c>
+      <c r="M1004" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1004" t="s">
+        <v>1271</v>
       </c>
     </row>
     <row r="1005" spans="1:14" x14ac:dyDescent="0.4">
@@ -16016,8 +16976,17 @@
       <c r="B1005" t="s">
         <v>7</v>
       </c>
-      <c r="D1005" t="s">
+      <c r="D1005" s="1" t="s">
         <v>660</v>
+      </c>
+      <c r="L1005" t="s">
+        <v>1270</v>
+      </c>
+      <c r="M1005" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1005" t="s">
+        <v>1272</v>
       </c>
     </row>
     <row r="1006" spans="1:14" x14ac:dyDescent="0.4">
@@ -16027,8 +16996,17 @@
       <c r="B1006" t="s">
         <v>7</v>
       </c>
-      <c r="D1006" t="s">
+      <c r="D1006" s="1" t="s">
         <v>669</v>
+      </c>
+      <c r="L1006" t="s">
+        <v>1270</v>
+      </c>
+      <c r="M1006" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1006" t="s">
+        <v>1273</v>
       </c>
     </row>
     <row r="1007" spans="1:14" x14ac:dyDescent="0.4">
@@ -16038,8 +17016,17 @@
       <c r="B1007" t="s">
         <v>7</v>
       </c>
-      <c r="D1007" t="s">
+      <c r="D1007" s="1" t="s">
         <v>671</v>
+      </c>
+      <c r="L1007" t="s">
+        <v>1274</v>
+      </c>
+      <c r="M1007" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1007" t="s">
+        <v>971</v>
       </c>
     </row>
     <row r="1008" spans="1:14" x14ac:dyDescent="0.4">
@@ -16049,308 +17036,542 @@
       <c r="B1008" t="s">
         <v>5</v>
       </c>
-      <c r="D1008" t="s">
+      <c r="D1008" s="1" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="1009" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1008" t="s">
+        <v>1274</v>
+      </c>
+      <c r="M1008" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1008" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1009" t="s">
         <v>670</v>
       </c>
       <c r="B1009" t="s">
         <v>5</v>
       </c>
-      <c r="D1009" t="s">
+      <c r="D1009" s="1" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="1010" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1009" t="s">
+        <v>1274</v>
+      </c>
+      <c r="M1009" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1009" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1010" t="s">
         <v>670</v>
       </c>
       <c r="B1010" t="s">
         <v>5</v>
       </c>
-      <c r="D1010" t="s">
+      <c r="D1010" s="1" t="s">
         <v>663</v>
       </c>
-    </row>
-    <row r="1011" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1010" t="s">
+        <v>1274</v>
+      </c>
+      <c r="M1010" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1010" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1011" t="s">
         <v>670</v>
       </c>
       <c r="B1011" t="s">
         <v>7</v>
       </c>
-      <c r="D1011" t="s">
+      <c r="D1011" s="1" t="s">
         <v>612</v>
       </c>
-    </row>
-    <row r="1012" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1011" t="s">
+        <v>1274</v>
+      </c>
+      <c r="M1011" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1011" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1012" t="s">
         <v>670</v>
       </c>
       <c r="B1012" t="s">
         <v>7</v>
       </c>
-      <c r="D1012" t="s">
+      <c r="D1012" s="1" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="1013" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1012" t="s">
+        <v>1274</v>
+      </c>
+      <c r="M1012" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1012" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1013" t="s">
         <v>672</v>
       </c>
       <c r="B1013" t="s">
         <v>5</v>
       </c>
-      <c r="D1013" t="s">
+      <c r="D1013" s="1" t="s">
         <v>593</v>
       </c>
-    </row>
-    <row r="1014" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1013" t="s">
+        <v>1156</v>
+      </c>
+      <c r="M1013" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1013" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1014" t="s">
         <v>672</v>
       </c>
       <c r="B1014" t="s">
         <v>7</v>
       </c>
-      <c r="D1014" t="s">
+      <c r="D1014" s="1" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="1015" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1014" t="s">
+        <v>1156</v>
+      </c>
+      <c r="M1014" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1014" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1015" t="s">
         <v>672</v>
       </c>
       <c r="B1015" t="s">
         <v>5</v>
       </c>
-      <c r="D1015" t="s">
+      <c r="D1015" s="1" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="1016" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1015" t="s">
+        <v>1156</v>
+      </c>
+      <c r="M1015" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1015" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1016" t="s">
         <v>672</v>
       </c>
       <c r="B1016" t="s">
         <v>5</v>
       </c>
-      <c r="D1016" t="s">
+      <c r="D1016" s="1" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="1017" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1016" t="s">
+        <v>1156</v>
+      </c>
+      <c r="M1016" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1016" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1017" t="s">
         <v>672</v>
       </c>
       <c r="B1017" t="s">
         <v>7</v>
       </c>
-      <c r="D1017" t="s">
+      <c r="D1017" s="1" t="s">
         <v>676</v>
       </c>
-    </row>
-    <row r="1018" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1017" t="s">
+        <v>1156</v>
+      </c>
+      <c r="M1017" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1017" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1018" t="s">
         <v>672</v>
       </c>
       <c r="B1018" t="s">
         <v>5</v>
       </c>
-      <c r="D1018" t="s">
+      <c r="D1018" s="1" t="s">
         <v>677</v>
       </c>
-    </row>
-    <row r="1019" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1018" t="s">
+        <v>1156</v>
+      </c>
+      <c r="M1018" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1018" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1019" t="s">
         <v>678</v>
       </c>
       <c r="B1019" t="s">
         <v>5</v>
       </c>
-      <c r="D1019" t="s">
+      <c r="D1019" s="1" t="s">
         <v>598</v>
       </c>
-    </row>
-    <row r="1020" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1019" t="s">
+        <v>1167</v>
+      </c>
+      <c r="M1019" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1019" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1020" t="s">
         <v>678</v>
       </c>
       <c r="B1020" t="s">
         <v>7</v>
       </c>
-      <c r="D1020" t="s">
+      <c r="D1020" s="1" t="s">
         <v>679</v>
       </c>
-    </row>
-    <row r="1021" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1020" t="s">
+        <v>1167</v>
+      </c>
+      <c r="M1020" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1020" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1021" t="s">
         <v>678</v>
       </c>
       <c r="B1021" t="s">
         <v>5</v>
       </c>
-      <c r="D1021" t="s">
+      <c r="D1021" s="1" t="s">
         <v>680</v>
       </c>
-    </row>
-    <row r="1022" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1021" t="s">
+        <v>1167</v>
+      </c>
+      <c r="M1021" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1021" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1022" t="s">
         <v>678</v>
       </c>
       <c r="B1022" t="s">
         <v>5</v>
       </c>
-      <c r="D1022" t="s">
+      <c r="D1022" s="1" t="s">
         <v>681</v>
       </c>
-    </row>
-    <row r="1023" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1022" t="s">
+        <v>1167</v>
+      </c>
+      <c r="M1022" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1022" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1023" t="s">
         <v>678</v>
       </c>
       <c r="B1023" t="s">
         <v>5</v>
       </c>
-      <c r="D1023" t="s">
+      <c r="D1023" s="1" t="s">
         <v>682</v>
       </c>
-    </row>
-    <row r="1024" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1023" t="s">
+        <v>1167</v>
+      </c>
+      <c r="M1023" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1023" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1024" t="s">
         <v>678</v>
       </c>
       <c r="B1024" t="s">
         <v>7</v>
       </c>
-      <c r="D1024" t="s">
+      <c r="D1024" s="1" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="1025" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1024" t="s">
+        <v>1167</v>
+      </c>
+      <c r="M1024" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1024" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1025" t="s">
         <v>678</v>
       </c>
       <c r="B1025" t="s">
         <v>5</v>
       </c>
-      <c r="D1025" t="s">
+      <c r="D1025" s="1" t="s">
         <v>684</v>
       </c>
-    </row>
-    <row r="1026" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1025" t="s">
+        <v>1167</v>
+      </c>
+      <c r="M1025" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1025" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1026" t="s">
         <v>685</v>
       </c>
       <c r="B1026" t="s">
         <v>5</v>
       </c>
-      <c r="D1026" t="s">
+      <c r="D1026" s="1" t="s">
         <v>604</v>
       </c>
-    </row>
-    <row r="1027" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1026" t="s">
+        <v>1173</v>
+      </c>
+      <c r="M1026" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1026" s="1" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1027" t="s">
         <v>685</v>
       </c>
       <c r="B1027" t="s">
         <v>7</v>
       </c>
-      <c r="D1027" t="s">
+      <c r="D1027" s="1" t="s">
         <v>686</v>
       </c>
-    </row>
-    <row r="1028" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1027" t="s">
+        <v>1173</v>
+      </c>
+      <c r="M1027" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1027" s="1" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1028" t="s">
         <v>685</v>
       </c>
       <c r="B1028" t="s">
         <v>7</v>
       </c>
-      <c r="D1028" t="s">
+      <c r="D1028" s="3" t="s">
         <v>687</v>
       </c>
-    </row>
-    <row r="1029" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1028" t="s">
+        <v>1173</v>
+      </c>
+      <c r="M1028" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1028" s="3" t="s">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1029" t="s">
         <v>685</v>
       </c>
       <c r="B1029" t="s">
         <v>7</v>
       </c>
-      <c r="D1029" t="s">
+      <c r="D1029" s="3" t="s">
         <v>688</v>
       </c>
-    </row>
-    <row r="1030" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1029" t="s">
+        <v>1173</v>
+      </c>
+      <c r="M1029" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1029" s="1" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1030" t="s">
         <v>685</v>
       </c>
       <c r="B1030" t="s">
         <v>7</v>
       </c>
-      <c r="D1030" t="s">
+      <c r="D1030" s="1" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="1031" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1030" t="s">
+        <v>1173</v>
+      </c>
+      <c r="M1030" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1030" s="1" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1031" t="s">
         <v>685</v>
       </c>
       <c r="B1031" t="s">
         <v>5</v>
       </c>
-      <c r="D1031" t="s">
+      <c r="D1031" s="1" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="1032" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1031" t="s">
+        <v>1173</v>
+      </c>
+      <c r="M1031" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1031" s="1" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1032" t="s">
         <v>685</v>
       </c>
       <c r="B1032" t="s">
         <v>7</v>
       </c>
-      <c r="D1032" t="s">
+      <c r="D1032" s="3" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="1033" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1032" t="s">
+        <v>1173</v>
+      </c>
+      <c r="M1032" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1032" s="3" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1033" t="s">
         <v>685</v>
       </c>
       <c r="B1033" t="s">
         <v>7</v>
       </c>
-      <c r="D1033" t="s">
+      <c r="D1033" s="3" t="s">
         <v>680</v>
       </c>
-    </row>
-    <row r="1034" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1033" t="s">
+        <v>1173</v>
+      </c>
+      <c r="M1033" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1033" s="1" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1034" t="s">
         <v>685</v>
       </c>
       <c r="B1034" t="s">
         <v>5</v>
       </c>
-      <c r="D1034" t="s">
+      <c r="D1034" s="1" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="1035" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1035" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1035" t="s">
         <v>685</v>
       </c>
       <c r="B1035" t="s">
         <v>5</v>
       </c>
-      <c r="D1035" t="s">
+      <c r="D1035" s="1" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="1036" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1036" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1036" t="s">
         <v>693</v>
       </c>
@@ -16360,8 +17581,17 @@
       <c r="D1036" t="s">
         <v>611</v>
       </c>
-    </row>
-    <row r="1037" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1036" t="s">
+        <v>1182</v>
+      </c>
+      <c r="M1036" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1036" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1037" t="s">
         <v>693</v>
       </c>
@@ -16371,8 +17601,17 @@
       <c r="D1037" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="1038" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1037" t="s">
+        <v>1182</v>
+      </c>
+      <c r="M1037" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1037" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1038" t="s">
         <v>693</v>
       </c>
@@ -16382,9 +17621,18 @@
       <c r="D1038" t="s">
         <v>695</v>
       </c>
-    </row>
-    <row r="1039" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A1039" t="s">
+      <c r="L1038" t="s">
+        <v>1182</v>
+      </c>
+      <c r="M1038" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1038" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A1039" s="2" t="s">
         <v>696</v>
       </c>
       <c r="B1039" t="s">
@@ -16394,810 +17642,1440 @@
         <v>615</v>
       </c>
     </row>
-    <row r="1040" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1040" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1040" t="s">
         <v>697</v>
       </c>
       <c r="B1040" t="s">
         <v>5</v>
       </c>
-      <c r="D1040" t="s">
+      <c r="D1040" s="1" t="s">
         <v>653</v>
       </c>
-    </row>
-    <row r="1041" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1040" t="s">
+        <v>1186</v>
+      </c>
+      <c r="M1040" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1040" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1041" t="s">
         <v>697</v>
       </c>
       <c r="B1041" t="s">
         <v>7</v>
       </c>
-      <c r="D1041" t="s">
+      <c r="D1041" s="1" t="s">
         <v>698</v>
       </c>
-    </row>
-    <row r="1042" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1041" t="s">
+        <v>1186</v>
+      </c>
+      <c r="M1041" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1041" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1042" t="s">
         <v>697</v>
       </c>
       <c r="B1042" t="s">
         <v>7</v>
       </c>
-      <c r="D1042" t="s">
+      <c r="D1042" s="1" t="s">
         <v>699</v>
       </c>
-    </row>
-    <row r="1043" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1042" t="s">
+        <v>1186</v>
+      </c>
+      <c r="M1042" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1042" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1043" t="s">
         <v>697</v>
       </c>
       <c r="B1043" t="s">
         <v>7</v>
       </c>
-      <c r="D1043" t="s">
+      <c r="D1043" s="1" t="s">
         <v>700</v>
       </c>
-    </row>
-    <row r="1044" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1043" t="s">
+        <v>1186</v>
+      </c>
+      <c r="M1043" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1043" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1044" t="s">
         <v>697</v>
       </c>
       <c r="B1044" t="s">
         <v>7</v>
       </c>
-      <c r="D1044" t="s">
+      <c r="D1044" s="1" t="s">
         <v>701</v>
       </c>
-    </row>
-    <row r="1045" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1044" t="s">
+        <v>1186</v>
+      </c>
+      <c r="M1044" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1044" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1045" t="s">
         <v>697</v>
       </c>
       <c r="B1045" t="s">
         <v>5</v>
       </c>
-      <c r="D1045" t="s">
+      <c r="D1045" s="1" t="s">
         <v>686</v>
       </c>
-    </row>
-    <row r="1046" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1045" t="s">
+        <v>1186</v>
+      </c>
+      <c r="M1045" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1045" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1046" t="s">
         <v>697</v>
       </c>
       <c r="B1046" t="s">
         <v>5</v>
       </c>
-      <c r="D1046" t="s">
+      <c r="D1046" s="1" t="s">
         <v>702</v>
       </c>
-    </row>
-    <row r="1047" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1046" t="s">
+        <v>1186</v>
+      </c>
+      <c r="M1046" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1046" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1047" t="s">
         <v>697</v>
       </c>
       <c r="B1047" t="s">
         <v>7</v>
       </c>
-      <c r="D1047" t="s">
+      <c r="D1047" s="1" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="1048" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1047" t="s">
+        <v>1186</v>
+      </c>
+      <c r="M1047" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1047" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1048" t="s">
         <v>697</v>
       </c>
       <c r="B1048" t="s">
         <v>5</v>
       </c>
-      <c r="D1048" t="s">
+      <c r="D1048" s="1" t="s">
         <v>703</v>
       </c>
-    </row>
-    <row r="1049" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1048" t="s">
+        <v>1186</v>
+      </c>
+      <c r="M1048" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1048" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1049" t="s">
         <v>704</v>
       </c>
       <c r="B1049" t="s">
         <v>5</v>
       </c>
-      <c r="D1049" t="s">
+      <c r="D1049" s="1" t="s">
         <v>662</v>
       </c>
-    </row>
-    <row r="1050" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1049" t="s">
+        <v>1196</v>
+      </c>
+      <c r="M1049" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1049" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1050" t="s">
         <v>704</v>
       </c>
       <c r="B1050" t="s">
         <v>5</v>
       </c>
-      <c r="D1050" t="s">
+      <c r="D1050" s="1" t="s">
         <v>700</v>
       </c>
-    </row>
-    <row r="1051" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1050" t="s">
+        <v>1196</v>
+      </c>
+      <c r="M1050" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1050" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1051" t="s">
         <v>704</v>
       </c>
       <c r="B1051" t="s">
         <v>5</v>
       </c>
-      <c r="D1051" t="s">
+      <c r="D1051" s="1" t="s">
         <v>687</v>
       </c>
-    </row>
-    <row r="1052" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1051" t="s">
+        <v>1196</v>
+      </c>
+      <c r="M1051" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1051" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1052" t="s">
         <v>704</v>
       </c>
       <c r="B1052" t="s">
         <v>7</v>
       </c>
-      <c r="D1052" t="s">
+      <c r="D1052" s="1" t="s">
         <v>705</v>
       </c>
-    </row>
-    <row r="1053" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1052" t="s">
+        <v>1196</v>
+      </c>
+      <c r="M1052" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1052" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1053" t="s">
         <v>704</v>
       </c>
       <c r="B1053" t="s">
         <v>7</v>
       </c>
-      <c r="D1053" t="s">
+      <c r="D1053" s="1" t="s">
         <v>682</v>
       </c>
-    </row>
-    <row r="1054" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1053" t="s">
+        <v>1196</v>
+      </c>
+      <c r="M1053" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1053" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1054" t="s">
         <v>704</v>
       </c>
       <c r="B1054" t="s">
         <v>5</v>
       </c>
-      <c r="D1054" t="s">
+      <c r="D1054" s="1" t="s">
         <v>706</v>
       </c>
-    </row>
-    <row r="1055" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1054" t="s">
+        <v>1196</v>
+      </c>
+      <c r="M1054" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1054" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1055" t="s">
         <v>707</v>
       </c>
       <c r="B1055" t="s">
         <v>5</v>
       </c>
-      <c r="D1055" t="s">
+      <c r="D1055" s="1" t="s">
         <v>665</v>
       </c>
-    </row>
-    <row r="1056" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1055" t="s">
+        <v>1216</v>
+      </c>
+      <c r="M1055" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1055" s="1" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1056" t="s">
         <v>707</v>
       </c>
       <c r="B1056" t="s">
         <v>5</v>
       </c>
-      <c r="D1056" t="s">
+      <c r="D1056" s="2" t="s">
         <v>698</v>
       </c>
-    </row>
-    <row r="1057" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1056" t="s">
+        <v>1216</v>
+      </c>
+      <c r="M1056" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1056" s="1" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1057" t="s">
         <v>707</v>
       </c>
       <c r="B1057" t="s">
         <v>7</v>
       </c>
-      <c r="D1057" t="s">
+      <c r="D1057" s="1" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="1058" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1058" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1058" t="s">
         <v>709</v>
       </c>
       <c r="B1058" t="s">
         <v>5</v>
       </c>
-      <c r="D1058" t="s">
+      <c r="D1058" s="1" t="s">
         <v>668</v>
       </c>
-    </row>
-    <row r="1059" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1058" t="s">
+        <v>1203</v>
+      </c>
+      <c r="M1058" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1058" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1059" t="s">
         <v>709</v>
       </c>
       <c r="B1059" t="s">
         <v>5</v>
       </c>
-      <c r="D1059" t="s">
+      <c r="D1059" s="1" t="s">
         <v>695</v>
       </c>
-    </row>
-    <row r="1060" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1059" t="s">
+        <v>1203</v>
+      </c>
+      <c r="M1059" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1059" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1060" t="s">
         <v>709</v>
       </c>
       <c r="B1060" t="s">
         <v>7</v>
       </c>
-      <c r="D1060" t="s">
+      <c r="D1060" s="1" t="s">
         <v>702</v>
       </c>
-    </row>
-    <row r="1061" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1060" t="s">
+        <v>1203</v>
+      </c>
+      <c r="M1060" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1060" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1061" t="s">
         <v>709</v>
       </c>
       <c r="B1061" t="s">
         <v>7</v>
       </c>
-      <c r="D1061" t="s">
+      <c r="D1061" s="1" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="1062" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1061" t="s">
+        <v>1203</v>
+      </c>
+      <c r="M1061" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1061" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1062" t="s">
         <v>711</v>
       </c>
       <c r="B1062" t="s">
         <v>5</v>
       </c>
-      <c r="D1062" t="s">
+      <c r="D1062" s="1" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="1063" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1062" t="s">
+        <v>1208</v>
+      </c>
+      <c r="M1062" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1062" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1063" t="s">
         <v>711</v>
       </c>
       <c r="B1063" t="s">
         <v>5</v>
       </c>
-      <c r="D1063" t="s">
+      <c r="D1063" s="1" t="s">
         <v>701</v>
       </c>
-    </row>
-    <row r="1064" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1063" t="s">
+        <v>1208</v>
+      </c>
+      <c r="M1063" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1063" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1064" t="s">
         <v>711</v>
       </c>
       <c r="B1064" t="s">
         <v>5</v>
       </c>
-      <c r="D1064" t="s">
+      <c r="D1064" s="1" t="s">
         <v>688</v>
       </c>
-    </row>
-    <row r="1065" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1064" t="s">
+        <v>1208</v>
+      </c>
+      <c r="M1064" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1064" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1065" t="s">
         <v>711</v>
       </c>
       <c r="B1065" t="s">
         <v>5</v>
       </c>
-      <c r="D1065" t="s">
+      <c r="D1065" s="1" t="s">
         <v>705</v>
       </c>
-    </row>
-    <row r="1066" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1065" t="s">
+        <v>1208</v>
+      </c>
+      <c r="M1065" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1065" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1066" t="s">
         <v>711</v>
       </c>
       <c r="B1066" t="s">
         <v>7</v>
       </c>
-      <c r="D1066" t="s">
+      <c r="D1066" s="1" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="1067" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1066" t="s">
+        <v>1208</v>
+      </c>
+      <c r="M1066" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1066" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1067" t="s">
         <v>711</v>
       </c>
       <c r="B1067" t="s">
         <v>7</v>
       </c>
-      <c r="D1067" t="s">
+      <c r="D1067" s="1" t="s">
         <v>681</v>
       </c>
-    </row>
-    <row r="1068" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1067" t="s">
+        <v>1208</v>
+      </c>
+      <c r="M1067" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1067" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1068" t="s">
         <v>711</v>
       </c>
       <c r="B1068" t="s">
         <v>5</v>
       </c>
-      <c r="D1068" t="s">
+      <c r="D1068" s="1" t="s">
         <v>712</v>
       </c>
-    </row>
-    <row r="1069" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1068" t="s">
+        <v>1208</v>
+      </c>
+      <c r="M1068" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1068" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1069" t="s">
         <v>713</v>
       </c>
       <c r="B1069" t="s">
         <v>7</v>
       </c>
-      <c r="D1069" t="s">
+      <c r="D1069" s="1" t="s">
         <v>703</v>
       </c>
-    </row>
-    <row r="1070" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1069" t="s">
+        <v>1151</v>
+      </c>
+      <c r="M1069" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1069" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1070" t="s">
         <v>713</v>
       </c>
       <c r="B1070" t="s">
         <v>7</v>
       </c>
-      <c r="D1070" t="s">
+      <c r="D1070" s="1" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="1071" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1070" t="s">
+        <v>1151</v>
+      </c>
+      <c r="M1070" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1070" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1071" t="s">
         <v>713</v>
       </c>
       <c r="B1071" t="s">
         <v>5</v>
       </c>
-      <c r="D1071" t="s">
+      <c r="D1071" s="1" t="s">
         <v>676</v>
       </c>
-    </row>
-    <row r="1072" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1071" t="s">
+        <v>1151</v>
+      </c>
+      <c r="M1071" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1071" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1072" t="s">
         <v>713</v>
       </c>
       <c r="B1072" t="s">
         <v>7</v>
       </c>
-      <c r="D1072" t="s">
+      <c r="D1072" s="1" t="s">
         <v>677</v>
       </c>
-    </row>
-    <row r="1073" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1072" t="s">
+        <v>1151</v>
+      </c>
+      <c r="M1072" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1072" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1073" t="s">
         <v>714</v>
       </c>
       <c r="B1073" t="s">
         <v>7</v>
       </c>
-      <c r="D1073" t="s">
+      <c r="D1073" s="1" t="s">
         <v>706</v>
       </c>
-    </row>
-    <row r="1074" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1073" t="s">
+        <v>1161</v>
+      </c>
+      <c r="M1073" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1073" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1074" t="s">
         <v>714</v>
       </c>
       <c r="B1074" t="s">
         <v>7</v>
       </c>
-      <c r="D1074" t="s">
+      <c r="D1074" s="1" t="s">
         <v>712</v>
       </c>
-    </row>
-    <row r="1075" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1074" t="s">
+        <v>1161</v>
+      </c>
+      <c r="M1074" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1074" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1075" t="s">
         <v>714</v>
       </c>
       <c r="B1075" t="s">
         <v>7</v>
       </c>
-      <c r="D1075" t="s">
+      <c r="D1075" s="1" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="1076" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1075" t="s">
+        <v>1161</v>
+      </c>
+      <c r="M1075" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1075" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1076" t="s">
         <v>714</v>
       </c>
       <c r="B1076" t="s">
         <v>5</v>
       </c>
-      <c r="D1076" t="s">
+      <c r="D1076" s="1" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="1077" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1076" t="s">
+        <v>1161</v>
+      </c>
+      <c r="M1076" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1076" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1077" t="s">
         <v>714</v>
       </c>
       <c r="B1077" t="s">
         <v>7</v>
       </c>
-      <c r="D1077" t="s">
+      <c r="D1077" s="1" t="s">
         <v>684</v>
       </c>
-    </row>
-    <row r="1078" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1077" t="s">
+        <v>1161</v>
+      </c>
+      <c r="M1077" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1077" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1078" t="s">
         <v>715</v>
       </c>
       <c r="B1078" t="s">
         <v>5</v>
       </c>
-      <c r="D1078" t="s">
+      <c r="D1078" s="1" t="s">
         <v>716</v>
       </c>
-    </row>
-    <row r="1079" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1078" t="s">
+        <v>1219</v>
+      </c>
+      <c r="M1078" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1078" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1079" t="s">
         <v>715</v>
       </c>
       <c r="B1079" t="s">
         <v>5</v>
       </c>
-      <c r="D1079" t="s">
+      <c r="D1079" s="1" t="s">
         <v>708</v>
       </c>
-    </row>
-    <row r="1080" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1079" t="s">
+        <v>1219</v>
+      </c>
+      <c r="M1079" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1079" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1080" t="s">
         <v>715</v>
       </c>
       <c r="B1080" t="s">
         <v>5</v>
       </c>
-      <c r="D1080" t="s">
+      <c r="D1080" s="1" t="s">
         <v>699</v>
       </c>
-    </row>
-    <row r="1081" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1080" t="s">
+        <v>1219</v>
+      </c>
+      <c r="M1080" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1080" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1081" t="s">
         <v>715</v>
       </c>
       <c r="B1081" t="s">
         <v>5</v>
       </c>
-      <c r="D1081" t="s">
+      <c r="D1081" s="1" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="1082" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1081" t="s">
+        <v>1219</v>
+      </c>
+      <c r="M1081" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1081" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1082" t="s">
         <v>715</v>
       </c>
       <c r="B1082" t="s">
         <v>5</v>
       </c>
-      <c r="D1082" t="s">
+      <c r="D1082" s="1" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="1083" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1082" t="s">
+        <v>1219</v>
+      </c>
+      <c r="M1082" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1082" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1083" t="s">
         <v>715</v>
       </c>
       <c r="B1083" t="s">
         <v>7</v>
       </c>
-      <c r="D1083" t="s">
+      <c r="D1083" s="1" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="1084" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1083" t="s">
+        <v>1219</v>
+      </c>
+      <c r="M1083" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1083" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1084" t="s">
         <v>715</v>
       </c>
       <c r="B1084" t="s">
         <v>7</v>
       </c>
-      <c r="D1084" t="s">
+      <c r="D1084" s="1" t="s">
         <v>717</v>
       </c>
-    </row>
-    <row r="1085" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1084" t="s">
+        <v>1219</v>
+      </c>
+      <c r="M1084" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1084" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1085" t="s">
         <v>715</v>
       </c>
       <c r="B1085" t="s">
         <v>7</v>
       </c>
-      <c r="D1085" t="s">
+      <c r="D1085" s="1" t="s">
         <v>718</v>
       </c>
-    </row>
-    <row r="1086" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1085" t="s">
+        <v>1219</v>
+      </c>
+      <c r="M1085" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1085" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1086" t="s">
         <v>715</v>
       </c>
       <c r="B1086" t="s">
         <v>5</v>
       </c>
-      <c r="D1086" t="s">
+      <c r="D1086" s="1" t="s">
         <v>719</v>
       </c>
-    </row>
-    <row r="1087" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1086" t="s">
+        <v>1219</v>
+      </c>
+      <c r="M1086" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1086" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1087" t="s">
         <v>720</v>
       </c>
       <c r="B1087" t="s">
         <v>5</v>
       </c>
-      <c r="D1087" t="s">
+      <c r="D1087" s="1" t="s">
         <v>718</v>
       </c>
-    </row>
-    <row r="1088" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1087" t="s">
+        <v>1229</v>
+      </c>
+      <c r="M1087" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1087" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1088" t="s">
         <v>720</v>
       </c>
       <c r="B1088" t="s">
         <v>7</v>
       </c>
-      <c r="D1088" t="s">
+      <c r="D1088" s="1" t="s">
         <v>719</v>
       </c>
-    </row>
-    <row r="1089" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1088" t="s">
+        <v>1229</v>
+      </c>
+      <c r="M1088" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1088" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1089" t="s">
         <v>721</v>
       </c>
       <c r="B1089" t="s">
         <v>7</v>
       </c>
-      <c r="D1089" t="s">
+      <c r="D1089" s="1" t="s">
         <v>716</v>
       </c>
-    </row>
-    <row r="1090" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1089" t="s">
+        <v>1232</v>
+      </c>
+      <c r="M1089" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1089" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1090" t="s">
         <v>721</v>
       </c>
       <c r="B1090" t="s">
         <v>5</v>
       </c>
-      <c r="D1090" t="s">
+      <c r="D1090" s="1" t="s">
         <v>722</v>
       </c>
-    </row>
-    <row r="1091" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1090" t="s">
+        <v>1232</v>
+      </c>
+      <c r="M1090" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1090" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1091" t="s">
         <v>721</v>
       </c>
       <c r="B1091" t="s">
         <v>5</v>
       </c>
-      <c r="D1091" t="s">
+      <c r="D1091" s="1" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="1092" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1091" t="s">
+        <v>1232</v>
+      </c>
+      <c r="M1091" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1091" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1092" t="s">
         <v>721</v>
       </c>
       <c r="B1092" t="s">
         <v>5</v>
       </c>
-      <c r="D1092" t="s">
+      <c r="D1092" s="1" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="1093" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1092" t="s">
+        <v>1232</v>
+      </c>
+      <c r="M1092" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1092" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1093" t="s">
         <v>721</v>
       </c>
       <c r="B1093" t="s">
         <v>5</v>
       </c>
-      <c r="D1093" t="s">
+      <c r="D1093" s="1" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="1094" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1093" t="s">
+        <v>1232</v>
+      </c>
+      <c r="M1093" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1093" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1094" t="s">
         <v>721</v>
       </c>
       <c r="B1094" t="s">
         <v>5</v>
       </c>
-      <c r="D1094" t="s">
+      <c r="D1094" s="1" t="s">
         <v>608</v>
       </c>
-    </row>
-    <row r="1095" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1094" t="s">
+        <v>1232</v>
+      </c>
+      <c r="M1094" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1094" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1095" t="s">
         <v>721</v>
       </c>
       <c r="B1095" t="s">
         <v>7</v>
       </c>
-      <c r="D1095" t="s">
+      <c r="D1095" s="1" t="s">
         <v>609</v>
       </c>
-    </row>
-    <row r="1096" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1095" t="s">
+        <v>1232</v>
+      </c>
+      <c r="M1095" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1095" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1096" t="s">
         <v>721</v>
       </c>
       <c r="B1096" t="s">
         <v>7</v>
       </c>
-      <c r="D1096" t="s">
+      <c r="D1096" s="1" t="s">
         <v>723</v>
       </c>
-    </row>
-    <row r="1097" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1096" t="s">
+        <v>1232</v>
+      </c>
+      <c r="M1096" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1096" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1097" t="s">
         <v>721</v>
       </c>
       <c r="B1097" t="s">
         <v>7</v>
       </c>
-      <c r="D1097" t="s">
+      <c r="D1097" s="1" t="s">
         <v>724</v>
       </c>
-    </row>
-    <row r="1098" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1097" t="s">
+        <v>1232</v>
+      </c>
+      <c r="M1097" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1097" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1098" t="s">
         <v>721</v>
       </c>
       <c r="B1098" t="s">
         <v>5</v>
       </c>
-      <c r="D1098" t="s">
+      <c r="D1098" s="1" t="s">
         <v>725</v>
       </c>
-    </row>
-    <row r="1099" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1098" t="s">
+        <v>1232</v>
+      </c>
+      <c r="M1098" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1098" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1099" t="s">
         <v>726</v>
       </c>
       <c r="B1099" t="s">
         <v>5</v>
       </c>
-      <c r="D1099" t="s">
+      <c r="D1099" s="1" t="s">
         <v>724</v>
       </c>
-    </row>
-    <row r="1100" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1099" t="s">
+        <v>1243</v>
+      </c>
+      <c r="M1099" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1099" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1100" t="s">
         <v>726</v>
       </c>
       <c r="B1100" t="s">
         <v>7</v>
       </c>
-      <c r="D1100" t="s">
+      <c r="D1100" s="1" t="s">
         <v>725</v>
       </c>
-    </row>
-    <row r="1101" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1100" t="s">
+        <v>1243</v>
+      </c>
+      <c r="M1100" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1100" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1101" t="s">
         <v>727</v>
       </c>
       <c r="B1101" t="s">
         <v>5</v>
       </c>
-      <c r="D1101" t="s">
+      <c r="D1101" s="1" t="s">
         <v>579</v>
       </c>
-    </row>
-    <row r="1102" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1101" t="s">
+        <v>1246</v>
+      </c>
+      <c r="M1101" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1101" s="1" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1102" t="s">
         <v>727</v>
       </c>
       <c r="B1102" t="s">
         <v>7</v>
       </c>
-      <c r="D1102" t="s">
+      <c r="D1102" s="1" t="s">
         <v>580</v>
       </c>
-    </row>
-    <row r="1103" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1102" t="s">
+        <v>1246</v>
+      </c>
+      <c r="M1102" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1102" s="1" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1103" t="s">
         <v>727</v>
       </c>
       <c r="B1103" t="s">
         <v>7</v>
       </c>
-      <c r="D1103" t="s">
+      <c r="D1103" s="1" t="s">
         <v>633</v>
       </c>
-    </row>
-    <row r="1104" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1103" t="s">
+        <v>1246</v>
+      </c>
+      <c r="M1103" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1103" s="1" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1104" t="s">
         <v>727</v>
       </c>
       <c r="B1104" t="s">
         <v>5</v>
       </c>
-      <c r="D1104" t="s">
+      <c r="D1104" s="1" t="s">
         <v>634</v>
       </c>
-    </row>
-    <row r="1105" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1104" t="s">
+        <v>1246</v>
+      </c>
+      <c r="M1104" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1104" s="1" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1105" t="s">
         <v>727</v>
       </c>
       <c r="B1105" t="s">
         <v>5</v>
       </c>
-      <c r="D1105" t="s">
+      <c r="D1105" s="2" t="s">
         <v>581</v>
       </c>
-    </row>
-    <row r="1106" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1105" t="s">
+        <v>1246</v>
+      </c>
+      <c r="M1105" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1105" s="1" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1106" t="s">
         <v>727</v>
       </c>
       <c r="B1106" t="s">
         <v>7</v>
       </c>
-      <c r="D1106" t="s">
+      <c r="D1106" s="2" t="s">
         <v>649</v>
       </c>
-    </row>
-    <row r="1107" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1106" t="s">
+        <v>1246</v>
+      </c>
+      <c r="M1106" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1106" s="1" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1107" t="s">
         <v>727</v>
       </c>
       <c r="B1107" t="s">
         <v>7</v>
       </c>
-      <c r="D1107" t="s">
+      <c r="D1107" s="1" t="s">
         <v>728</v>
       </c>
-    </row>
-    <row r="1108" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1107" t="s">
+        <v>1246</v>
+      </c>
+      <c r="M1107" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1107" s="1" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1108" t="s">
         <v>727</v>
       </c>
       <c r="B1108" t="s">
         <v>7</v>
       </c>
-      <c r="D1108" t="s">
+      <c r="D1108" s="1" t="s">
         <v>729</v>
       </c>
     </row>
-    <row r="1109" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1109" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1109" t="s">
         <v>727</v>
       </c>
       <c r="B1109" t="s">
         <v>7</v>
       </c>
-      <c r="D1109" t="s">
+      <c r="D1109" s="1" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="1110" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1110" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1110" t="s">
         <v>731</v>
       </c>
       <c r="B1110" t="s">
         <v>7</v>
       </c>
-      <c r="D1110" t="s">
+      <c r="D1110" s="1" t="s">
         <v>732</v>
       </c>
-    </row>
-    <row r="1111" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1110" t="s">
+        <v>1251</v>
+      </c>
+      <c r="M1110" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1110" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1111" t="s">
         <v>731</v>
       </c>
       <c r="B1111" t="s">
         <v>5</v>
       </c>
-      <c r="D1111" t="s">
+      <c r="D1111" s="1" t="s">
         <v>730</v>
       </c>
-    </row>
-    <row r="1112" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1111" t="s">
+        <v>1251</v>
+      </c>
+      <c r="M1111" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1111" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1112" t="s">
         <v>731</v>
       </c>
       <c r="B1112" t="s">
         <v>7</v>
       </c>
-      <c r="D1112" t="s">
+      <c r="D1112" s="1" t="s">
         <v>733</v>
       </c>
-    </row>
-    <row r="1113" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1112" t="s">
+        <v>1251</v>
+      </c>
+      <c r="M1112" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1112" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1113" t="s">
         <v>734</v>
       </c>
@@ -17208,7 +19086,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="1114" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1114" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1114" t="s">
         <v>734</v>
       </c>
@@ -17219,29 +19097,47 @@
         <v>735</v>
       </c>
     </row>
-    <row r="1115" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1115" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1115" t="s">
         <v>736</v>
       </c>
       <c r="B1115" t="s">
         <v>5</v>
       </c>
-      <c r="D1115" t="s">
+      <c r="D1115" s="1" t="s">
         <v>732</v>
       </c>
-    </row>
-    <row r="1116" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1115" t="s">
+        <v>1254</v>
+      </c>
+      <c r="M1115" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1115" s="1" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1116" t="s">
         <v>737</v>
       </c>
       <c r="B1116" t="s">
         <v>5</v>
       </c>
-      <c r="D1116" t="s">
+      <c r="D1116" s="2" t="s">
         <v>733</v>
       </c>
-    </row>
-    <row r="1117" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1116" s="2" t="s">
+        <v>1254</v>
+      </c>
+      <c r="M1116" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1116" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1117" t="s">
         <v>738</v>
       </c>
@@ -17252,7 +19148,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="1118" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1118" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1118" t="s">
         <v>738</v>
       </c>
@@ -17263,7 +19159,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="1119" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1119" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1119" t="s">
         <v>738</v>
       </c>
@@ -17274,7 +19170,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="1120" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1120" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1120" t="s">
         <v>738</v>
       </c>
@@ -17413,7 +19309,7 @@
       <c r="B1132" t="s">
         <v>5</v>
       </c>
-      <c r="D1132" t="s">
+      <c r="D1132" s="2" t="s">
         <v>744</v>
       </c>
     </row>
@@ -17637,7 +19533,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="1153" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1153" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1153" t="s">
         <v>760</v>
       </c>
@@ -17648,7 +19544,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1154" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1154" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1154" t="s">
         <v>760</v>
       </c>
@@ -17659,7 +19555,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="1155" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1155" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1155" t="s">
         <v>760</v>
       </c>
@@ -17670,7 +19566,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="1156" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1156" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1156" t="s">
         <v>760</v>
       </c>
@@ -17681,7 +19577,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="1157" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1157" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1157" t="s">
         <v>760</v>
       </c>
@@ -17692,7 +19588,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="1158" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1158" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1158" t="s">
         <v>764</v>
       </c>
@@ -17703,7 +19599,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="1159" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1159" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1159" t="s">
         <v>764</v>
       </c>
@@ -17714,7 +19610,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="1160" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1160" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1160" t="s">
         <v>764</v>
       </c>
@@ -17725,7 +19621,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="1161" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1161" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1161" t="s">
         <v>767</v>
       </c>
@@ -17736,7 +19632,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="1162" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1162" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1162" t="s">
         <v>767</v>
       </c>
@@ -17747,7 +19643,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="1163" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1163" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1163" t="s">
         <v>769</v>
       </c>
@@ -17758,7 +19654,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="1164" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1164" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1164" t="s">
         <v>770</v>
       </c>
@@ -17769,7 +19665,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="1165" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1165" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1165" t="s">
         <v>771</v>
       </c>
@@ -17779,8 +19675,17 @@
       <c r="D1165" t="s">
         <v>639</v>
       </c>
-    </row>
-    <row r="1166" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1165" t="s">
+        <v>1122</v>
+      </c>
+      <c r="M1165" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1165" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1166" t="s">
         <v>771</v>
       </c>
@@ -17790,19 +19695,28 @@
       <c r="D1166" t="s">
         <v>640</v>
       </c>
-    </row>
-    <row r="1167" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1166" t="s">
+        <v>1122</v>
+      </c>
+      <c r="M1166" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1166" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1167" t="s">
         <v>771</v>
       </c>
       <c r="B1167" t="s">
         <v>5</v>
       </c>
-      <c r="D1167" t="s">
+      <c r="D1167" s="2" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="1168" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1168" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1168" t="s">
         <v>771</v>
       </c>
@@ -17812,8 +19726,17 @@
       <c r="D1168" t="s">
         <v>772</v>
       </c>
-    </row>
-    <row r="1169" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1168" t="s">
+        <v>1122</v>
+      </c>
+      <c r="M1168" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1168" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1169" t="s">
         <v>771</v>
       </c>
@@ -17823,8 +19746,17 @@
       <c r="D1169" t="s">
         <v>773</v>
       </c>
-    </row>
-    <row r="1170" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1169" t="s">
+        <v>1122</v>
+      </c>
+      <c r="M1169" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1169" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1170" t="s">
         <v>771</v>
       </c>
@@ -17834,261 +19766,276 @@
       <c r="D1170" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="1171" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1170" t="s">
+        <v>1122</v>
+      </c>
+      <c r="M1170" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1170" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1171" t="s">
         <v>771</v>
       </c>
       <c r="B1171" t="s">
         <v>7</v>
       </c>
-      <c r="D1171" t="s">
+      <c r="D1171" s="2" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="1172" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1171" t="s">
+        <v>1122</v>
+      </c>
+      <c r="M1171" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1172" t="s">
         <v>771</v>
       </c>
       <c r="B1172" t="s">
         <v>7</v>
       </c>
-      <c r="D1172" t="s">
+      <c r="D1172" s="2" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="1173" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1173" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1173" t="s">
         <v>771</v>
       </c>
       <c r="B1173" t="s">
         <v>7</v>
       </c>
-      <c r="D1173" t="s">
+      <c r="D1173" s="2" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="1174" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1174" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1174" t="s">
         <v>771</v>
       </c>
       <c r="B1174" t="s">
         <v>7</v>
       </c>
-      <c r="D1174" t="s">
+      <c r="D1174" s="2" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="1175" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1175" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1175" t="s">
         <v>771</v>
       </c>
       <c r="B1175" t="s">
         <v>7</v>
       </c>
-      <c r="D1175" t="s">
+      <c r="D1175" s="2" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="1176" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1176" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1176" t="s">
         <v>771</v>
       </c>
       <c r="B1176" t="s">
         <v>7</v>
       </c>
-      <c r="D1176" t="s">
+      <c r="D1176" s="2" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="1177" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1177" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1177" t="s">
         <v>771</v>
       </c>
       <c r="B1177" t="s">
         <v>7</v>
       </c>
-      <c r="D1177" t="s">
+      <c r="D1177" s="2" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="1178" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1178" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1178" t="s">
         <v>771</v>
       </c>
       <c r="B1178" t="s">
         <v>7</v>
       </c>
-      <c r="D1178" t="s">
+      <c r="D1178" s="2" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="1179" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1179" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1179" t="s">
         <v>771</v>
       </c>
       <c r="B1179" t="s">
         <v>7</v>
       </c>
-      <c r="D1179" t="s">
+      <c r="D1179" s="2" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="1180" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1180" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1180" t="s">
         <v>771</v>
       </c>
       <c r="B1180" t="s">
         <v>7</v>
       </c>
-      <c r="D1180" t="s">
+      <c r="D1180" s="2" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="1181" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1181" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1181" t="s">
         <v>771</v>
       </c>
       <c r="B1181" t="s">
         <v>7</v>
       </c>
-      <c r="D1181" t="s">
+      <c r="D1181" s="2" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="1182" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1182" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1182" t="s">
         <v>771</v>
       </c>
       <c r="B1182" t="s">
         <v>7</v>
       </c>
-      <c r="D1182" t="s">
+      <c r="D1182" s="2" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="1183" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1183" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1183" t="s">
         <v>771</v>
       </c>
       <c r="B1183" t="s">
         <v>7</v>
       </c>
-      <c r="D1183" t="s">
+      <c r="D1183" s="2" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="1184" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1184" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1184" t="s">
         <v>771</v>
       </c>
       <c r="B1184" t="s">
         <v>7</v>
       </c>
-      <c r="D1184" t="s">
+      <c r="D1184" s="2" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="1185" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1185" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1185" t="s">
         <v>771</v>
       </c>
       <c r="B1185" t="s">
         <v>7</v>
       </c>
-      <c r="D1185" t="s">
+      <c r="D1185" s="2" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="1186" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1186" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1186" t="s">
         <v>771</v>
       </c>
       <c r="B1186" t="s">
         <v>7</v>
       </c>
-      <c r="D1186" t="s">
+      <c r="D1186" s="2" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="1187" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1187" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1187" t="s">
         <v>771</v>
       </c>
       <c r="B1187" t="s">
         <v>7</v>
       </c>
-      <c r="D1187" t="s">
+      <c r="D1187" s="2" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="1188" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1188" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1188" t="s">
         <v>771</v>
       </c>
       <c r="B1188" t="s">
         <v>7</v>
       </c>
-      <c r="D1188" t="s">
+      <c r="D1188" s="2" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="1189" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1189" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1189" t="s">
         <v>771</v>
       </c>
       <c r="B1189" t="s">
         <v>7</v>
       </c>
-      <c r="D1189" t="s">
+      <c r="D1189" s="2" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="1190" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1190" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1190" t="s">
         <v>771</v>
       </c>
       <c r="B1190" t="s">
         <v>7</v>
       </c>
-      <c r="D1190" t="s">
+      <c r="D1190" s="2" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="1191" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1191" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1191" t="s">
         <v>771</v>
       </c>
       <c r="B1191" t="s">
         <v>7</v>
       </c>
-      <c r="D1191" t="s">
+      <c r="D1191" s="2" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="1192" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1192" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1192" t="s">
         <v>771</v>
       </c>
       <c r="B1192" t="s">
         <v>7</v>
       </c>
-      <c r="D1192" t="s">
+      <c r="D1192" s="2" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="1193" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1193" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1193" t="s">
         <v>771</v>
       </c>
       <c r="B1193" t="s">
         <v>7</v>
       </c>
-      <c r="D1193" t="s">
+      <c r="D1193" s="2" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="1194" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1194" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1194" t="s">
         <v>771</v>
       </c>
@@ -18098,63 +20045,111 @@
       <c r="D1194" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="1195" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="N1194" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1195" t="s">
         <v>775</v>
       </c>
       <c r="B1195" t="s">
         <v>7</v>
       </c>
-      <c r="D1195" t="s">
+      <c r="D1195" s="1" t="s">
         <v>776</v>
       </c>
-    </row>
-    <row r="1196" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1195" t="s">
+        <v>1128</v>
+      </c>
+      <c r="M1195" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1195" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1196" t="s">
         <v>775</v>
       </c>
       <c r="B1196" t="s">
         <v>5</v>
       </c>
-      <c r="D1196" t="s">
+      <c r="D1196" s="1" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="1197" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1196" t="s">
+        <v>1128</v>
+      </c>
+      <c r="M1196" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1196" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1197" t="s">
         <v>775</v>
       </c>
       <c r="B1197" t="s">
         <v>7</v>
       </c>
-      <c r="D1197" t="s">
+      <c r="D1197" s="1" t="s">
         <v>777</v>
       </c>
-    </row>
-    <row r="1198" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1197" t="s">
+        <v>1128</v>
+      </c>
+      <c r="M1197" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1197" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1198" t="s">
         <v>778</v>
       </c>
       <c r="B1198" t="s">
         <v>5</v>
       </c>
-      <c r="D1198" t="s">
+      <c r="D1198" s="1" t="s">
         <v>772</v>
       </c>
-    </row>
-    <row r="1199" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1198" t="s">
+        <v>1131</v>
+      </c>
+      <c r="M1198" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1198" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1199" t="s">
         <v>778</v>
       </c>
       <c r="B1199" t="s">
         <v>7</v>
       </c>
-      <c r="D1199" t="s">
+      <c r="D1199" s="1" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="1200" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1199" t="s">
+        <v>1131</v>
+      </c>
+      <c r="M1199" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1199" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1200" t="s">
         <v>780</v>
       </c>
@@ -18164,8 +20159,17 @@
       <c r="D1200" t="s">
         <v>776</v>
       </c>
-    </row>
-    <row r="1201" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1200" t="s">
+        <v>1134</v>
+      </c>
+      <c r="M1200" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1200" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1201" t="s">
         <v>781</v>
       </c>
@@ -18175,140 +20179,257 @@
       <c r="D1201" t="s">
         <v>777</v>
       </c>
-    </row>
-    <row r="1202" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1201" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="M1201" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1201" s="2" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1202" t="s">
         <v>782</v>
       </c>
       <c r="B1202" t="s">
         <v>7</v>
       </c>
-      <c r="D1202" t="s">
+      <c r="D1202" s="1" t="s">
         <v>783</v>
       </c>
-    </row>
-    <row r="1203" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1202" t="s">
+        <v>1137</v>
+      </c>
+      <c r="M1202" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1202" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1203" t="s">
         <v>782</v>
       </c>
       <c r="B1203" t="s">
         <v>5</v>
       </c>
-      <c r="D1203" t="s">
+      <c r="D1203" s="1" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="1204" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1203" t="s">
+        <v>1137</v>
+      </c>
+      <c r="M1203" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1203" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1204" t="s">
         <v>782</v>
       </c>
       <c r="B1204" t="s">
         <v>5</v>
       </c>
-      <c r="D1204" t="s">
+      <c r="D1204" s="1" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="1205" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1204" t="s">
+        <v>1137</v>
+      </c>
+      <c r="M1204" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1204" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1205" t="s">
         <v>782</v>
       </c>
       <c r="B1205" t="s">
         <v>5</v>
       </c>
-      <c r="D1205" t="s">
+      <c r="D1205" s="1" t="s">
         <v>523</v>
       </c>
-    </row>
-    <row r="1206" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1205" t="s">
+        <v>1137</v>
+      </c>
+      <c r="M1205" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1205" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1206" t="s">
         <v>782</v>
       </c>
       <c r="B1206" t="s">
         <v>5</v>
       </c>
-      <c r="D1206" t="s">
+      <c r="D1206" s="1" t="s">
         <v>538</v>
       </c>
-    </row>
-    <row r="1207" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1206" t="s">
+        <v>1137</v>
+      </c>
+      <c r="M1206" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1206" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1207" t="s">
         <v>782</v>
       </c>
       <c r="B1207" t="s">
         <v>5</v>
       </c>
-      <c r="D1207" t="s">
+      <c r="D1207" s="1" t="s">
         <v>553</v>
       </c>
-    </row>
-    <row r="1208" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1207" t="s">
+        <v>1137</v>
+      </c>
+      <c r="M1207" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1207" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1208" t="s">
         <v>782</v>
       </c>
       <c r="B1208" t="s">
         <v>5</v>
       </c>
-      <c r="D1208" t="s">
+      <c r="D1208" s="1" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="1209" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1208" t="s">
+        <v>1137</v>
+      </c>
+      <c r="M1208" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1208" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1209" t="s">
         <v>782</v>
       </c>
       <c r="B1209" t="s">
         <v>7</v>
       </c>
-      <c r="D1209" t="s">
+      <c r="D1209" s="1" t="s">
         <v>784</v>
       </c>
-    </row>
-    <row r="1210" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1209" t="s">
+        <v>1137</v>
+      </c>
+      <c r="M1209" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1209" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1210" t="s">
         <v>785</v>
       </c>
       <c r="B1210" t="s">
         <v>7</v>
       </c>
-      <c r="D1210" t="s">
+      <c r="D1210" s="1" t="s">
         <v>786</v>
       </c>
-    </row>
-    <row r="1211" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1210" t="s">
+        <v>1150</v>
+      </c>
+      <c r="M1210" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1210" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1211" t="s">
         <v>787</v>
       </c>
       <c r="B1211" t="s">
         <v>5</v>
       </c>
-      <c r="D1211" t="s">
+      <c r="D1211" s="1" t="s">
         <v>783</v>
       </c>
-    </row>
-    <row r="1212" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1211" t="s">
+        <v>1145</v>
+      </c>
+      <c r="M1211" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1211" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1212" t="s">
         <v>787</v>
       </c>
       <c r="B1212" t="s">
         <v>7</v>
       </c>
-      <c r="D1212" t="s">
+      <c r="D1212" s="1" t="s">
         <v>788</v>
       </c>
-    </row>
-    <row r="1213" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1212" t="s">
+        <v>1145</v>
+      </c>
+      <c r="M1212" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1212" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1213" t="s">
         <v>789</v>
       </c>
       <c r="B1213" t="s">
         <v>5</v>
       </c>
-      <c r="D1213" t="s">
+      <c r="D1213" s="1" t="s">
         <v>786</v>
       </c>
-    </row>
-    <row r="1214" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1213" t="s">
+        <v>1148</v>
+      </c>
+      <c r="M1213" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1213" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1214" t="s">
         <v>790</v>
       </c>
@@ -18318,8 +20439,17 @@
       <c r="D1214" t="s">
         <v>617</v>
       </c>
-    </row>
-    <row r="1215" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1214" t="s">
+        <v>1257</v>
+      </c>
+      <c r="M1214" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1214" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1215" t="s">
         <v>790</v>
       </c>
@@ -18329,8 +20459,17 @@
       <c r="D1215" t="s">
         <v>618</v>
       </c>
-    </row>
-    <row r="1216" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1215" t="s">
+        <v>1257</v>
+      </c>
+      <c r="M1215" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1215" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1216" t="s">
         <v>790</v>
       </c>
@@ -18340,8 +20479,17 @@
       <c r="D1216" t="s">
         <v>619</v>
       </c>
-    </row>
-    <row r="1217" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1216" t="s">
+        <v>1257</v>
+      </c>
+      <c r="M1216" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1216" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1217" t="s">
         <v>790</v>
       </c>
@@ -18351,8 +20499,17 @@
       <c r="D1217" t="s">
         <v>620</v>
       </c>
-    </row>
-    <row r="1218" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1217" t="s">
+        <v>1257</v>
+      </c>
+      <c r="M1217" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1217" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1218" t="s">
         <v>790</v>
       </c>
@@ -18362,8 +20519,17 @@
       <c r="D1218" t="s">
         <v>641</v>
       </c>
-    </row>
-    <row r="1219" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1218" t="s">
+        <v>1257</v>
+      </c>
+      <c r="M1218" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1218" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1219" t="s">
         <v>790</v>
       </c>
@@ -18373,8 +20539,17 @@
       <c r="D1219" t="s">
         <v>642</v>
       </c>
-    </row>
-    <row r="1220" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1219" t="s">
+        <v>1257</v>
+      </c>
+      <c r="M1219" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1219" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1220" t="s">
         <v>790</v>
       </c>
@@ -18384,8 +20559,17 @@
       <c r="D1220" t="s">
         <v>791</v>
       </c>
-    </row>
-    <row r="1221" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1220" t="s">
+        <v>1257</v>
+      </c>
+      <c r="M1220" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1220" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1221" t="s">
         <v>790</v>
       </c>
@@ -18395,8 +20579,17 @@
       <c r="D1221" t="s">
         <v>792</v>
       </c>
-    </row>
-    <row r="1222" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="L1221" t="s">
+        <v>1257</v>
+      </c>
+      <c r="M1221" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1221" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1222" t="s">
         <v>790</v>
       </c>
@@ -18407,7 +20600,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="1223" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1223" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1223" t="s">
         <v>794</v>
       </c>
@@ -18418,7 +20611,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="1224" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1224" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1224" t="s">
         <v>794</v>
       </c>
@@ -18429,7 +20622,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="1225" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1225" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1225" t="s">
         <v>794</v>
       </c>
@@ -18440,7 +20633,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="1226" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1226" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1226" t="s">
         <v>797</v>
       </c>
@@ -18451,7 +20644,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="1227" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1227" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1227" t="s">
         <v>797</v>
       </c>
@@ -18462,7 +20655,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="1228" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1228" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1228" t="s">
         <v>799</v>
       </c>
@@ -18473,7 +20666,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="1229" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1229" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1229" t="s">
         <v>800</v>
       </c>
@@ -18484,7 +20677,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="1230" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1230" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1230" t="s">
         <v>801</v>
       </c>
@@ -18495,7 +20688,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="1231" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1231" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1231" t="s">
         <v>801</v>
       </c>
@@ -18506,7 +20699,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="1232" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1232" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1232" t="s">
         <v>801</v>
       </c>
@@ -19889,13 +22082,13 @@
         <v>162</v>
       </c>
       <c r="L1351" t="s">
-        <v>1027</v>
+        <v>1037</v>
       </c>
       <c r="M1351" t="s">
         <v>7</v>
       </c>
       <c r="N1351" t="s">
-        <v>1028</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="1352" spans="1:14" x14ac:dyDescent="0.4">
@@ -19909,13 +22102,13 @@
         <v>598</v>
       </c>
       <c r="L1352" t="s">
-        <v>1027</v>
+        <v>1037</v>
       </c>
       <c r="M1352" t="s">
         <v>7</v>
       </c>
       <c r="N1352" t="s">
-        <v>1029</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="1353" spans="1:14" x14ac:dyDescent="0.4">
@@ -19929,13 +22122,13 @@
         <v>888</v>
       </c>
       <c r="L1353" t="s">
-        <v>1027</v>
+        <v>1037</v>
       </c>
       <c r="M1353" t="s">
         <v>5</v>
       </c>
       <c r="N1353" t="s">
-        <v>1030</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="1354" spans="1:14" x14ac:dyDescent="0.4">
@@ -19949,13 +22142,13 @@
         <v>889</v>
       </c>
       <c r="L1354" t="s">
-        <v>1027</v>
+        <v>1037</v>
       </c>
       <c r="M1354" t="s">
         <v>5</v>
       </c>
       <c r="N1354" t="s">
-        <v>1031</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="1355" spans="1:14" x14ac:dyDescent="0.4">
@@ -19969,13 +22162,13 @@
         <v>890</v>
       </c>
       <c r="L1355" t="s">
-        <v>1027</v>
+        <v>1037</v>
       </c>
       <c r="M1355" t="s">
         <v>5</v>
       </c>
       <c r="N1355" t="s">
-        <v>1032</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="1356" spans="1:14" x14ac:dyDescent="0.4">
@@ -19989,13 +22182,13 @@
         <v>891</v>
       </c>
       <c r="L1356" t="s">
-        <v>1027</v>
+        <v>1037</v>
       </c>
       <c r="M1356" t="s">
         <v>7</v>
       </c>
       <c r="N1356" t="s">
-        <v>1033</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="1357" spans="1:14" x14ac:dyDescent="0.4">
@@ -20009,7 +22202,7 @@
         <v>892</v>
       </c>
       <c r="L1357" t="s">
-        <v>1027</v>
+        <v>1037</v>
       </c>
       <c r="M1357" t="s">
         <v>7</v>
@@ -20029,7 +22222,7 @@
         <v>893</v>
       </c>
       <c r="L1358" t="s">
-        <v>1027</v>
+        <v>1037</v>
       </c>
       <c r="M1358" t="s">
         <v>5</v>
@@ -20049,13 +22242,13 @@
         <v>168</v>
       </c>
       <c r="L1359" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="M1359" t="s">
         <v>7</v>
       </c>
       <c r="N1359" s="1" t="s">
-        <v>1018</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="1360" spans="1:14" x14ac:dyDescent="0.4">
@@ -20069,13 +22262,13 @@
         <v>604</v>
       </c>
       <c r="L1360" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="M1360" t="s">
         <v>7</v>
       </c>
       <c r="N1360" s="1" t="s">
-        <v>1019</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="1361" spans="1:14" x14ac:dyDescent="0.4">
@@ -20089,13 +22282,13 @@
         <v>895</v>
       </c>
       <c r="L1361" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="M1361" t="s">
         <v>5</v>
       </c>
       <c r="N1361" s="1" t="s">
-        <v>1020</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="1362" spans="1:14" x14ac:dyDescent="0.4">
@@ -20109,13 +22302,13 @@
         <v>896</v>
       </c>
       <c r="L1362" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="M1362" t="s">
         <v>5</v>
       </c>
       <c r="N1362" s="1" t="s">
-        <v>1021</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="1363" spans="1:14" x14ac:dyDescent="0.4">
@@ -20129,13 +22322,13 @@
         <v>897</v>
       </c>
       <c r="L1363" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="M1363" t="s">
         <v>7</v>
       </c>
       <c r="N1363" s="3" t="s">
-        <v>1022</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="1364" spans="1:14" x14ac:dyDescent="0.4">
@@ -20149,13 +22342,13 @@
         <v>898</v>
       </c>
       <c r="L1364" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="M1364" t="s">
         <v>5</v>
       </c>
       <c r="N1364" s="1" t="s">
-        <v>1023</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="1365" spans="1:14" x14ac:dyDescent="0.4">
@@ -20169,13 +22362,13 @@
         <v>899</v>
       </c>
       <c r="L1365" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="M1365" t="s">
         <v>7</v>
       </c>
       <c r="N1365" s="1" t="s">
-        <v>1024</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="1366" spans="1:14" x14ac:dyDescent="0.4">
@@ -20189,13 +22382,13 @@
         <v>884</v>
       </c>
       <c r="L1366" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="M1366" t="s">
         <v>7</v>
       </c>
       <c r="N1366" s="5" t="s">
-        <v>1025</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="1367" spans="1:14" x14ac:dyDescent="0.4">
@@ -20209,13 +22402,13 @@
         <v>889</v>
       </c>
       <c r="L1367" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="M1367" t="s">
         <v>7</v>
       </c>
       <c r="N1367" s="4" t="s">
-        <v>1026</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="1368" spans="1:14" x14ac:dyDescent="0.4">
@@ -20251,13 +22444,13 @@
         <v>175</v>
       </c>
       <c r="L1370" t="s">
-        <v>1012</v>
+        <v>1022</v>
       </c>
       <c r="M1370" t="s">
         <v>7</v>
       </c>
       <c r="N1370" t="s">
-        <v>1013</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="1371" spans="1:14" x14ac:dyDescent="0.4">
@@ -20271,13 +22464,13 @@
         <v>611</v>
       </c>
       <c r="L1371" t="s">
-        <v>1012</v>
+        <v>1022</v>
       </c>
       <c r="M1371" t="s">
         <v>7</v>
       </c>
       <c r="N1371" t="s">
-        <v>1014</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="1372" spans="1:14" x14ac:dyDescent="0.4">
@@ -20291,13 +22484,13 @@
         <v>903</v>
       </c>
       <c r="L1372" t="s">
-        <v>1012</v>
+        <v>1022</v>
       </c>
       <c r="M1372" t="s">
         <v>5</v>
       </c>
       <c r="N1372" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="1373" spans="1:14" x14ac:dyDescent="0.4">
@@ -20311,13 +22504,13 @@
         <v>904</v>
       </c>
       <c r="L1373" t="s">
-        <v>1012</v>
+        <v>1022</v>
       </c>
       <c r="M1373" t="s">
         <v>7</v>
       </c>
       <c r="N1373" t="s">
-        <v>1016</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="1374" spans="1:14" x14ac:dyDescent="0.4">
@@ -20419,13 +22612,13 @@
         <v>399</v>
       </c>
       <c r="L1382" s="2" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
       <c r="M1382" s="2" t="s">
         <v>5</v>
       </c>
       <c r="N1382" s="2" t="s">
-        <v>1010</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="1383" spans="1:14" x14ac:dyDescent="0.4">
@@ -20439,13 +22632,13 @@
         <v>410</v>
       </c>
       <c r="L1383" s="2" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
       <c r="M1383" s="2" t="s">
         <v>7</v>
       </c>
       <c r="N1383" s="2" t="s">
-        <v>1011</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="1384" spans="1:14" x14ac:dyDescent="0.4">
@@ -21639,7 +23832,7 @@
         <v>5</v>
       </c>
       <c r="N1485" t="s">
-        <v>1006</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="1486" spans="1:14" x14ac:dyDescent="0.4">
@@ -21659,7 +23852,7 @@
         <v>7</v>
       </c>
       <c r="N1486" t="s">
-        <v>1007</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="1487" spans="1:14" x14ac:dyDescent="0.4">
@@ -22285,7 +24478,7 @@
       <c r="B1525" t="s">
         <v>5</v>
       </c>
-      <c r="D1525" t="s">
+      <c r="D1525" s="1" t="s">
         <v>926</v>
       </c>
       <c r="L1525" t="s">
@@ -22305,7 +24498,7 @@
       <c r="B1526" t="s">
         <v>7</v>
       </c>
-      <c r="D1526" t="s">
+      <c r="D1526" s="1" t="s">
         <v>927</v>
       </c>
       <c r="L1526" t="s">
@@ -22903,6 +25096,9 @@
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="N907:N953">
+    <sortCondition ref="N907:N953"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>